--- a/excel_templates/HojaGastosMartin(baseRaftxo).xlsx
+++ b/excel_templates/HojaGastosMartin(baseRaftxo).xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\userRafae\Descargas\martin_gastos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\userRafae\Descargas\martin_gastos\web_app\excel_templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72762575-2279-4672-A37C-E115A04B1905}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00D3B304-95B2-4C79-B977-D9AEBC010588}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BF93DF72-C9B7-484A-B310-BDC1682097D2}"/>
   </bookViews>
@@ -980,19 +980,211 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1004,20 +1196,92 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1031,275 +1295,11 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1745,129 +1745,129 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:44" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C1" s="84" t="s">
+      <c r="C1" s="43" t="s">
         <v>35</v>
       </c>
-      <c r="D1" s="84"/>
-      <c r="E1" s="99" t="s">
+      <c r="D1" s="43"/>
+      <c r="E1" s="78" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="100"/>
-      <c r="G1" s="100"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
       <c r="H1" s="5"/>
-      <c r="I1" s="84" t="s">
+      <c r="I1" s="43" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="84"/>
-      <c r="K1" s="84"/>
-      <c r="L1" s="101" t="s">
+      <c r="J1" s="43"/>
+      <c r="K1" s="43"/>
+      <c r="L1" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="M1" s="101"/>
-      <c r="N1" s="101"/>
-      <c r="O1" s="101"/>
-      <c r="P1" s="101"/>
-      <c r="Q1" s="84" t="s">
+      <c r="M1" s="41"/>
+      <c r="N1" s="41"/>
+      <c r="O1" s="41"/>
+      <c r="P1" s="41"/>
+      <c r="Q1" s="43" t="s">
         <v>37</v>
       </c>
-      <c r="R1" s="84"/>
-      <c r="S1" s="84"/>
-      <c r="T1" s="84"/>
-      <c r="U1" s="82" t="s">
+      <c r="R1" s="43"/>
+      <c r="S1" s="43"/>
+      <c r="T1" s="43"/>
+      <c r="U1" s="80" t="s">
         <v>44</v>
       </c>
-      <c r="V1" s="83"/>
-      <c r="W1" s="83"/>
-      <c r="Y1" s="84" t="s">
+      <c r="V1" s="81"/>
+      <c r="W1" s="81"/>
+      <c r="Y1" s="43" t="s">
         <v>38</v>
       </c>
-      <c r="Z1" s="84"/>
-      <c r="AA1" s="84"/>
-      <c r="AB1" s="84"/>
-      <c r="AC1" s="82" t="s">
+      <c r="Z1" s="43"/>
+      <c r="AA1" s="43"/>
+      <c r="AB1" s="43"/>
+      <c r="AC1" s="80" t="s">
         <v>44</v>
       </c>
-      <c r="AD1" s="83"/>
-      <c r="AE1" s="83"/>
-      <c r="AF1" s="83"/>
-      <c r="AG1" s="83"/>
+      <c r="AD1" s="81"/>
+      <c r="AE1" s="81"/>
+      <c r="AF1" s="81"/>
+      <c r="AG1" s="81"/>
       <c r="AH1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="AI1" s="101"/>
-      <c r="AJ1" s="101"/>
-      <c r="AK1" s="101"/>
+      <c r="AI1" s="41"/>
+      <c r="AJ1" s="41"/>
+      <c r="AK1" s="41"/>
       <c r="AL1" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AM1" s="101"/>
-      <c r="AN1" s="101"/>
+      <c r="AM1" s="41"/>
+      <c r="AN1" s="41"/>
       <c r="AO1" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="98"/>
-      <c r="AQ1" s="98"/>
-      <c r="AR1" s="98"/>
+      <c r="AP1" s="42"/>
+      <c r="AQ1" s="42"/>
+      <c r="AR1" s="42"/>
     </row>
     <row r="2" spans="1:44" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:44" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="AH3" s="41" t="s">
+      <c r="AH3" s="129" t="s">
         <v>21</v>
       </c>
-      <c r="AI3" s="42"/>
-      <c r="AJ3" s="43" t="s">
+      <c r="AI3" s="130"/>
+      <c r="AJ3" s="131" t="s">
         <v>23</v>
       </c>
-      <c r="AK3" s="44"/>
-      <c r="AL3" s="41" t="s">
+      <c r="AK3" s="132"/>
+      <c r="AL3" s="129" t="s">
         <v>22</v>
       </c>
-      <c r="AM3" s="42"/>
+      <c r="AM3" s="130"/>
     </row>
     <row r="4" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="102"/>
-      <c r="B4" s="103"/>
-      <c r="C4" s="103"/>
-      <c r="D4" s="104"/>
+      <c r="A4" s="128"/>
+      <c r="B4" s="112"/>
+      <c r="C4" s="112"/>
+      <c r="D4" s="113"/>
       <c r="E4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="105"/>
-      <c r="G4" s="105"/>
-      <c r="H4" s="105"/>
-      <c r="I4" s="105"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="28"/>
       <c r="J4" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="106"/>
-      <c r="L4" s="106"/>
-      <c r="M4" s="106"/>
-      <c r="N4" s="106"/>
-      <c r="O4" s="106"/>
-      <c r="P4" s="106"/>
-      <c r="Q4" s="106"/>
-      <c r="R4" s="106"/>
-      <c r="S4" s="106"/>
-      <c r="T4" s="106"/>
-      <c r="U4" s="106"/>
-      <c r="V4" s="106"/>
-      <c r="W4" s="106"/>
-      <c r="X4" s="47" t="s">
+      <c r="K4" s="133"/>
+      <c r="L4" s="133"/>
+      <c r="M4" s="133"/>
+      <c r="N4" s="133"/>
+      <c r="O4" s="133"/>
+      <c r="P4" s="133"/>
+      <c r="Q4" s="133"/>
+      <c r="R4" s="133"/>
+      <c r="S4" s="133"/>
+      <c r="T4" s="133"/>
+      <c r="U4" s="133"/>
+      <c r="V4" s="133"/>
+      <c r="W4" s="133"/>
+      <c r="X4" s="108" t="s">
         <v>15</v>
       </c>
-      <c r="Y4" s="47" t="s">
+      <c r="Y4" s="108" t="s">
         <v>16</v>
       </c>
-      <c r="Z4" s="47" t="s">
+      <c r="Z4" s="108" t="s">
         <v>17</v>
       </c>
-      <c r="AA4" s="47" t="s">
+      <c r="AA4" s="108" t="s">
         <v>18</v>
       </c>
-      <c r="AB4" s="47" t="s">
+      <c r="AB4" s="108" t="s">
         <v>0</v>
       </c>
-      <c r="AC4" s="47" t="s">
+      <c r="AC4" s="108" t="s">
         <v>19</v>
       </c>
       <c r="AD4" s="12"/>
@@ -1882,58 +1882,58 @@
       </c>
       <c r="AH4" s="14"/>
       <c r="AI4" s="15"/>
-      <c r="AJ4" s="45" t="s">
+      <c r="AJ4" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="AK4" s="46"/>
-      <c r="AL4" s="72"/>
-      <c r="AM4" s="73"/>
-      <c r="AN4" s="76" t="s">
+      <c r="AK4" s="52"/>
+      <c r="AL4" s="68"/>
+      <c r="AM4" s="69"/>
+      <c r="AN4" s="72" t="s">
         <v>31</v>
       </c>
-      <c r="AO4" s="63"/>
-      <c r="AP4" s="63"/>
-      <c r="AQ4" s="50"/>
-      <c r="AR4" s="51"/>
+      <c r="AO4" s="65"/>
+      <c r="AP4" s="65"/>
+      <c r="AQ4" s="44"/>
+      <c r="AR4" s="45"/>
     </row>
     <row r="5" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="30" t="s">
+      <c r="A5" s="115" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="28"/>
-      <c r="C5" s="28" t="s">
+      <c r="B5" s="116"/>
+      <c r="C5" s="116" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="29"/>
+      <c r="D5" s="117"/>
       <c r="E5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="107"/>
-      <c r="G5" s="107"/>
-      <c r="H5" s="107"/>
-      <c r="I5" s="107"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="29"/>
+      <c r="H5" s="29"/>
+      <c r="I5" s="29"/>
       <c r="J5" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="K5" s="108"/>
-      <c r="L5" s="108"/>
-      <c r="M5" s="108"/>
-      <c r="N5" s="108"/>
-      <c r="O5" s="108"/>
-      <c r="P5" s="108"/>
-      <c r="Q5" s="108"/>
-      <c r="R5" s="108"/>
-      <c r="S5" s="108"/>
-      <c r="T5" s="108"/>
-      <c r="U5" s="108"/>
-      <c r="V5" s="108"/>
-      <c r="W5" s="108"/>
-      <c r="X5" s="48"/>
-      <c r="Y5" s="48"/>
-      <c r="Z5" s="48"/>
-      <c r="AA5" s="48"/>
-      <c r="AB5" s="48"/>
-      <c r="AC5" s="48"/>
+      <c r="K5" s="134"/>
+      <c r="L5" s="134"/>
+      <c r="M5" s="134"/>
+      <c r="N5" s="134"/>
+      <c r="O5" s="134"/>
+      <c r="P5" s="134"/>
+      <c r="Q5" s="134"/>
+      <c r="R5" s="134"/>
+      <c r="S5" s="134"/>
+      <c r="T5" s="134"/>
+      <c r="U5" s="134"/>
+      <c r="V5" s="134"/>
+      <c r="W5" s="134"/>
+      <c r="X5" s="109"/>
+      <c r="Y5" s="109"/>
+      <c r="Z5" s="109"/>
+      <c r="AA5" s="109"/>
+      <c r="AB5" s="109"/>
+      <c r="AC5" s="109"/>
       <c r="AE5" s="7">
         <v>2</v>
       </c>
@@ -1945,35 +1945,35 @@
       </c>
       <c r="AH5" s="14"/>
       <c r="AI5" s="15"/>
-      <c r="AJ5" s="45" t="s">
+      <c r="AJ5" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="AK5" s="46"/>
-      <c r="AL5" s="74"/>
-      <c r="AM5" s="75"/>
-      <c r="AN5" s="77"/>
+      <c r="AK5" s="52"/>
+      <c r="AL5" s="70"/>
+      <c r="AM5" s="71"/>
+      <c r="AN5" s="73"/>
       <c r="AO5" s="64"/>
       <c r="AP5" s="64"/>
-      <c r="AQ5" s="52"/>
-      <c r="AR5" s="53"/>
+      <c r="AQ5" s="66"/>
+      <c r="AR5" s="67"/>
     </row>
     <row r="6" spans="1:44" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="109"/>
-      <c r="B6" s="110"/>
-      <c r="C6" s="111"/>
-      <c r="D6" s="112"/>
-      <c r="E6" s="38" t="s">
+      <c r="A6" s="124"/>
+      <c r="B6" s="125"/>
+      <c r="C6" s="126"/>
+      <c r="D6" s="127"/>
+      <c r="E6" s="107" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="38"/>
-      <c r="G6" s="38"/>
-      <c r="H6" s="38"/>
-      <c r="X6" s="49"/>
-      <c r="Y6" s="49"/>
-      <c r="Z6" s="49"/>
-      <c r="AA6" s="49"/>
-      <c r="AB6" s="49"/>
-      <c r="AC6" s="49"/>
+      <c r="F6" s="107"/>
+      <c r="G6" s="107"/>
+      <c r="H6" s="107"/>
+      <c r="X6" s="110"/>
+      <c r="Y6" s="110"/>
+      <c r="Z6" s="110"/>
+      <c r="AA6" s="110"/>
+      <c r="AB6" s="110"/>
+      <c r="AC6" s="110"/>
       <c r="AE6" s="7">
         <v>3</v>
       </c>
@@ -1985,56 +1985,56 @@
       </c>
       <c r="AH6" s="14"/>
       <c r="AI6" s="15"/>
-      <c r="AJ6" s="45" t="s">
+      <c r="AJ6" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="AK6" s="46"/>
+      <c r="AK6" s="52"/>
       <c r="AL6" s="14"/>
       <c r="AM6" s="15"/>
-      <c r="AN6" s="78" t="s">
+      <c r="AN6" s="86" t="s">
         <v>32</v>
       </c>
-      <c r="AO6" s="65"/>
-      <c r="AP6" s="65"/>
-      <c r="AQ6" s="52"/>
-      <c r="AR6" s="53"/>
+      <c r="AO6" s="63"/>
+      <c r="AP6" s="63"/>
+      <c r="AQ6" s="66"/>
+      <c r="AR6" s="67"/>
     </row>
     <row r="7" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="33" t="s">
+      <c r="A7" s="97" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="31" t="s">
+      <c r="B7" s="100" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="31"/>
-      <c r="D7" s="32"/>
-      <c r="E7" s="113"/>
-      <c r="F7" s="113"/>
-      <c r="G7" s="113"/>
-      <c r="H7" s="113"/>
-      <c r="I7" s="113"/>
-      <c r="J7" s="113"/>
-      <c r="K7" s="113"/>
-      <c r="M7" s="40" t="s">
+      <c r="C7" s="100"/>
+      <c r="D7" s="101"/>
+      <c r="E7" s="119"/>
+      <c r="F7" s="119"/>
+      <c r="G7" s="119"/>
+      <c r="H7" s="119"/>
+      <c r="I7" s="119"/>
+      <c r="J7" s="119"/>
+      <c r="K7" s="119"/>
+      <c r="M7" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="N7" s="40"/>
-      <c r="O7" s="107"/>
-      <c r="P7" s="107"/>
-      <c r="Q7" s="107"/>
-      <c r="R7" s="107"/>
-      <c r="S7" s="107"/>
-      <c r="T7" s="107"/>
-      <c r="V7" s="37" t="s">
+      <c r="N7" s="61"/>
+      <c r="O7" s="29"/>
+      <c r="P7" s="29"/>
+      <c r="Q7" s="29"/>
+      <c r="R7" s="29"/>
+      <c r="S7" s="29"/>
+      <c r="T7" s="29"/>
+      <c r="V7" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="W7" s="37"/>
-      <c r="X7" s="107"/>
-      <c r="Y7" s="107"/>
-      <c r="Z7" s="107"/>
-      <c r="AA7" s="107"/>
-      <c r="AB7" s="107"/>
-      <c r="AC7" s="107"/>
+      <c r="W7" s="62"/>
+      <c r="X7" s="29"/>
+      <c r="Y7" s="29"/>
+      <c r="Z7" s="29"/>
+      <c r="AA7" s="29"/>
+      <c r="AB7" s="29"/>
+      <c r="AC7" s="29"/>
       <c r="AE7" s="7">
         <v>4</v>
       </c>
@@ -2046,50 +2046,50 @@
       </c>
       <c r="AH7" s="14"/>
       <c r="AI7" s="15"/>
-      <c r="AJ7" s="45" t="s">
+      <c r="AJ7" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="AK7" s="46"/>
+      <c r="AK7" s="52"/>
       <c r="AL7" s="14"/>
       <c r="AM7" s="15"/>
-      <c r="AN7" s="79"/>
+      <c r="AN7" s="87"/>
       <c r="AO7" s="64"/>
       <c r="AP7" s="64"/>
-      <c r="AQ7" s="54"/>
-      <c r="AR7" s="55"/>
+      <c r="AQ7" s="46"/>
+      <c r="AR7" s="47"/>
     </row>
     <row r="8" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="34"/>
-      <c r="B8" s="114"/>
-      <c r="C8" s="114"/>
-      <c r="D8" s="115"/>
-      <c r="E8" s="113"/>
-      <c r="F8" s="113"/>
-      <c r="G8" s="113"/>
-      <c r="H8" s="113"/>
-      <c r="I8" s="113"/>
-      <c r="J8" s="113"/>
-      <c r="K8" s="113"/>
-      <c r="M8" s="40" t="s">
+      <c r="A8" s="98"/>
+      <c r="B8" s="120"/>
+      <c r="C8" s="120"/>
+      <c r="D8" s="121"/>
+      <c r="E8" s="119"/>
+      <c r="F8" s="119"/>
+      <c r="G8" s="119"/>
+      <c r="H8" s="119"/>
+      <c r="I8" s="119"/>
+      <c r="J8" s="119"/>
+      <c r="K8" s="119"/>
+      <c r="M8" s="61" t="s">
         <v>5</v>
       </c>
-      <c r="N8" s="40"/>
-      <c r="O8" s="107"/>
-      <c r="P8" s="107"/>
-      <c r="Q8" s="107"/>
-      <c r="R8" s="107"/>
-      <c r="S8" s="107"/>
-      <c r="T8" s="107"/>
-      <c r="V8" s="37" t="s">
+      <c r="N8" s="61"/>
+      <c r="O8" s="29"/>
+      <c r="P8" s="29"/>
+      <c r="Q8" s="29"/>
+      <c r="R8" s="29"/>
+      <c r="S8" s="29"/>
+      <c r="T8" s="29"/>
+      <c r="V8" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="W8" s="37"/>
-      <c r="X8" s="107"/>
-      <c r="Y8" s="107"/>
-      <c r="Z8" s="107"/>
-      <c r="AA8" s="107"/>
-      <c r="AB8" s="107"/>
-      <c r="AC8" s="107"/>
+      <c r="W8" s="62"/>
+      <c r="X8" s="29"/>
+      <c r="Y8" s="29"/>
+      <c r="Z8" s="29"/>
+      <c r="AA8" s="29"/>
+      <c r="AB8" s="29"/>
+      <c r="AC8" s="29"/>
       <c r="AE8" s="7">
         <v>5</v>
       </c>
@@ -2099,82 +2099,82 @@
       <c r="AG8" s="17"/>
       <c r="AH8" s="14"/>
       <c r="AI8" s="15"/>
-      <c r="AJ8" s="45" t="s">
+      <c r="AJ8" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="AK8" s="46"/>
+      <c r="AK8" s="52"/>
       <c r="AL8" s="14"/>
       <c r="AM8" s="15"/>
-      <c r="AN8" s="80"/>
-      <c r="AO8" s="66" t="s">
+      <c r="AN8" s="53"/>
+      <c r="AO8" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="AP8" s="67"/>
-      <c r="AQ8" s="56"/>
-      <c r="AR8" s="57"/>
+      <c r="AP8" s="38"/>
+      <c r="AQ8" s="57"/>
+      <c r="AR8" s="58"/>
     </row>
     <row r="9" spans="1:44" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="34"/>
-      <c r="B9" s="114"/>
-      <c r="C9" s="114"/>
-      <c r="D9" s="115"/>
-      <c r="E9" s="113"/>
-      <c r="F9" s="113"/>
-      <c r="G9" s="113"/>
-      <c r="H9" s="113"/>
-      <c r="I9" s="113"/>
-      <c r="J9" s="113"/>
-      <c r="K9" s="113"/>
-      <c r="M9" s="40" t="s">
+      <c r="A9" s="98"/>
+      <c r="B9" s="120"/>
+      <c r="C9" s="120"/>
+      <c r="D9" s="121"/>
+      <c r="E9" s="119"/>
+      <c r="F9" s="119"/>
+      <c r="G9" s="119"/>
+      <c r="H9" s="119"/>
+      <c r="I9" s="119"/>
+      <c r="J9" s="119"/>
+      <c r="K9" s="119"/>
+      <c r="M9" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="N9" s="40"/>
-      <c r="O9" s="116"/>
-      <c r="P9" s="116"/>
-      <c r="Q9" s="107"/>
-      <c r="R9" s="107"/>
-      <c r="S9" s="107"/>
-      <c r="T9" s="107"/>
-      <c r="V9" s="37" t="s">
+      <c r="N9" s="61"/>
+      <c r="O9" s="30"/>
+      <c r="P9" s="30"/>
+      <c r="Q9" s="29"/>
+      <c r="R9" s="29"/>
+      <c r="S9" s="29"/>
+      <c r="T9" s="29"/>
+      <c r="V9" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="W9" s="37"/>
-      <c r="X9" s="107"/>
-      <c r="Y9" s="107"/>
-      <c r="Z9" s="107"/>
-      <c r="AA9" s="107"/>
-      <c r="AB9" s="107"/>
-      <c r="AC9" s="107"/>
+      <c r="W9" s="62"/>
+      <c r="X9" s="29"/>
+      <c r="Y9" s="29"/>
+      <c r="Z9" s="29"/>
+      <c r="AA9" s="29"/>
+      <c r="AB9" s="29"/>
+      <c r="AC9" s="29"/>
       <c r="AG9" s="17"/>
       <c r="AH9" s="14"/>
       <c r="AI9" s="15"/>
-      <c r="AJ9" s="45" t="s">
+      <c r="AJ9" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="AK9" s="46"/>
+      <c r="AK9" s="52"/>
       <c r="AL9" s="14"/>
       <c r="AM9" s="15"/>
-      <c r="AN9" s="81"/>
-      <c r="AO9" s="68"/>
-      <c r="AP9" s="69"/>
-      <c r="AQ9" s="58"/>
-      <c r="AR9" s="59"/>
+      <c r="AN9" s="54"/>
+      <c r="AO9" s="55"/>
+      <c r="AP9" s="56"/>
+      <c r="AQ9" s="59"/>
+      <c r="AR9" s="60"/>
     </row>
     <row r="10" spans="1:44" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="35"/>
-      <c r="B10" s="117"/>
-      <c r="C10" s="117"/>
-      <c r="D10" s="118"/>
-      <c r="E10" s="36" t="s">
+      <c r="A10" s="99"/>
+      <c r="B10" s="122"/>
+      <c r="C10" s="122"/>
+      <c r="D10" s="123"/>
+      <c r="E10" s="88" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="36"/>
-      <c r="G10" s="39"/>
-      <c r="H10" s="39"/>
-      <c r="I10" s="39"/>
-      <c r="J10" s="39"/>
-      <c r="K10" s="39"/>
-      <c r="L10" s="39"/>
+      <c r="F10" s="88"/>
+      <c r="G10" s="89"/>
+      <c r="H10" s="89"/>
+      <c r="I10" s="89"/>
+      <c r="J10" s="89"/>
+      <c r="K10" s="89"/>
+      <c r="L10" s="89"/>
       <c r="M10" s="18"/>
       <c r="N10" s="18"/>
       <c r="O10" s="18"/>
@@ -2198,64 +2198,64 @@
       <c r="AG10" s="20"/>
       <c r="AH10" s="21"/>
       <c r="AI10" s="22"/>
-      <c r="AJ10" s="70" t="s">
+      <c r="AJ10" s="90" t="s">
         <v>30</v>
       </c>
-      <c r="AK10" s="71"/>
+      <c r="AK10" s="91"/>
       <c r="AL10" s="21"/>
       <c r="AM10" s="22"/>
       <c r="AN10" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="AO10" s="60"/>
-      <c r="AP10" s="61"/>
-      <c r="AQ10" s="61"/>
-      <c r="AR10" s="62"/>
+      <c r="AO10" s="48"/>
+      <c r="AP10" s="49"/>
+      <c r="AQ10" s="49"/>
+      <c r="AR10" s="50"/>
     </row>
     <row r="11" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="102"/>
-      <c r="B11" s="103"/>
-      <c r="C11" s="103"/>
-      <c r="D11" s="104"/>
+      <c r="A11" s="128"/>
+      <c r="B11" s="112"/>
+      <c r="C11" s="112"/>
+      <c r="D11" s="113"/>
       <c r="E11" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F11" s="105"/>
-      <c r="G11" s="105"/>
-      <c r="H11" s="105"/>
-      <c r="I11" s="105"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="28"/>
       <c r="J11" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="K11" s="119"/>
-      <c r="L11" s="119"/>
-      <c r="M11" s="119"/>
-      <c r="N11" s="119"/>
-      <c r="O11" s="119"/>
-      <c r="P11" s="119"/>
-      <c r="Q11" s="119"/>
-      <c r="R11" s="119"/>
-      <c r="S11" s="119"/>
-      <c r="T11" s="119"/>
-      <c r="U11" s="119"/>
-      <c r="V11" s="119"/>
-      <c r="W11" s="119"/>
-      <c r="X11" s="47" t="s">
+      <c r="K11" s="133"/>
+      <c r="L11" s="133"/>
+      <c r="M11" s="133"/>
+      <c r="N11" s="133"/>
+      <c r="O11" s="133"/>
+      <c r="P11" s="133"/>
+      <c r="Q11" s="133"/>
+      <c r="R11" s="133"/>
+      <c r="S11" s="133"/>
+      <c r="T11" s="133"/>
+      <c r="U11" s="133"/>
+      <c r="V11" s="133"/>
+      <c r="W11" s="133"/>
+      <c r="X11" s="108" t="s">
         <v>15</v>
       </c>
-      <c r="Y11" s="47" t="s">
+      <c r="Y11" s="108" t="s">
         <v>16</v>
       </c>
-      <c r="Z11" s="47" t="s">
+      <c r="Z11" s="108" t="s">
         <v>17</v>
       </c>
-      <c r="AA11" s="47" t="s">
+      <c r="AA11" s="108" t="s">
         <v>18</v>
       </c>
-      <c r="AB11" s="47" t="s">
+      <c r="AB11" s="108" t="s">
         <v>0</v>
       </c>
-      <c r="AC11" s="47" t="s">
+      <c r="AC11" s="108" t="s">
         <v>19</v>
       </c>
       <c r="AD11" s="12"/>
@@ -2270,58 +2270,58 @@
       </c>
       <c r="AH11" s="14"/>
       <c r="AI11" s="15"/>
-      <c r="AJ11" s="45" t="s">
+      <c r="AJ11" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="AK11" s="46"/>
-      <c r="AL11" s="72"/>
-      <c r="AM11" s="73"/>
-      <c r="AN11" s="76" t="s">
+      <c r="AK11" s="52"/>
+      <c r="AL11" s="68"/>
+      <c r="AM11" s="69"/>
+      <c r="AN11" s="72" t="s">
         <v>31</v>
       </c>
-      <c r="AO11" s="63"/>
-      <c r="AP11" s="63"/>
-      <c r="AQ11" s="50"/>
-      <c r="AR11" s="51"/>
+      <c r="AO11" s="65"/>
+      <c r="AP11" s="65"/>
+      <c r="AQ11" s="44"/>
+      <c r="AR11" s="45"/>
     </row>
     <row r="12" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="30" t="s">
+      <c r="A12" s="115" t="s">
         <v>1</v>
       </c>
-      <c r="B12" s="28"/>
-      <c r="C12" s="28" t="s">
+      <c r="B12" s="116"/>
+      <c r="C12" s="116" t="s">
         <v>2</v>
       </c>
-      <c r="D12" s="29"/>
+      <c r="D12" s="117"/>
       <c r="E12" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F12" s="107"/>
-      <c r="G12" s="107"/>
-      <c r="H12" s="107"/>
-      <c r="I12" s="107"/>
+      <c r="F12" s="29"/>
+      <c r="G12" s="29"/>
+      <c r="H12" s="29"/>
+      <c r="I12" s="29"/>
       <c r="J12" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="K12" s="120"/>
-      <c r="L12" s="120"/>
-      <c r="M12" s="120"/>
-      <c r="N12" s="120"/>
-      <c r="O12" s="120"/>
-      <c r="P12" s="120"/>
-      <c r="Q12" s="120"/>
-      <c r="R12" s="120"/>
-      <c r="S12" s="120"/>
-      <c r="T12" s="120"/>
-      <c r="U12" s="120"/>
-      <c r="V12" s="120"/>
-      <c r="W12" s="120"/>
-      <c r="X12" s="48"/>
-      <c r="Y12" s="48"/>
-      <c r="Z12" s="48"/>
-      <c r="AA12" s="48"/>
-      <c r="AB12" s="48"/>
-      <c r="AC12" s="48"/>
+      <c r="K12" s="134"/>
+      <c r="L12" s="134"/>
+      <c r="M12" s="134"/>
+      <c r="N12" s="134"/>
+      <c r="O12" s="134"/>
+      <c r="P12" s="134"/>
+      <c r="Q12" s="134"/>
+      <c r="R12" s="134"/>
+      <c r="S12" s="134"/>
+      <c r="T12" s="134"/>
+      <c r="U12" s="134"/>
+      <c r="V12" s="134"/>
+      <c r="W12" s="134"/>
+      <c r="X12" s="109"/>
+      <c r="Y12" s="109"/>
+      <c r="Z12" s="109"/>
+      <c r="AA12" s="109"/>
+      <c r="AB12" s="109"/>
+      <c r="AC12" s="109"/>
       <c r="AE12" s="7">
         <v>2</v>
       </c>
@@ -2333,35 +2333,35 @@
       </c>
       <c r="AH12" s="14"/>
       <c r="AI12" s="15"/>
-      <c r="AJ12" s="45" t="s">
+      <c r="AJ12" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="AK12" s="46"/>
-      <c r="AL12" s="74"/>
-      <c r="AM12" s="75"/>
-      <c r="AN12" s="77"/>
+      <c r="AK12" s="52"/>
+      <c r="AL12" s="70"/>
+      <c r="AM12" s="71"/>
+      <c r="AN12" s="73"/>
       <c r="AO12" s="64"/>
       <c r="AP12" s="64"/>
-      <c r="AQ12" s="52"/>
-      <c r="AR12" s="53"/>
+      <c r="AQ12" s="66"/>
+      <c r="AR12" s="67"/>
     </row>
     <row r="13" spans="1:44" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="109"/>
-      <c r="B13" s="110"/>
-      <c r="C13" s="111"/>
-      <c r="D13" s="112"/>
-      <c r="E13" s="38" t="s">
+      <c r="A13" s="124"/>
+      <c r="B13" s="125"/>
+      <c r="C13" s="126"/>
+      <c r="D13" s="127"/>
+      <c r="E13" s="107" t="s">
         <v>10</v>
       </c>
-      <c r="F13" s="38"/>
-      <c r="G13" s="38"/>
-      <c r="H13" s="38"/>
-      <c r="X13" s="49"/>
-      <c r="Y13" s="49"/>
-      <c r="Z13" s="49"/>
-      <c r="AA13" s="49"/>
-      <c r="AB13" s="49"/>
-      <c r="AC13" s="49"/>
+      <c r="F13" s="107"/>
+      <c r="G13" s="107"/>
+      <c r="H13" s="107"/>
+      <c r="X13" s="110"/>
+      <c r="Y13" s="110"/>
+      <c r="Z13" s="110"/>
+      <c r="AA13" s="110"/>
+      <c r="AB13" s="110"/>
+      <c r="AC13" s="110"/>
       <c r="AE13" s="7">
         <v>3</v>
       </c>
@@ -2373,56 +2373,56 @@
       </c>
       <c r="AH13" s="14"/>
       <c r="AI13" s="15"/>
-      <c r="AJ13" s="45" t="s">
+      <c r="AJ13" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="AK13" s="46"/>
+      <c r="AK13" s="52"/>
       <c r="AL13" s="14"/>
       <c r="AM13" s="15"/>
-      <c r="AN13" s="78" t="s">
+      <c r="AN13" s="86" t="s">
         <v>32</v>
       </c>
-      <c r="AO13" s="65"/>
-      <c r="AP13" s="65"/>
-      <c r="AQ13" s="52"/>
-      <c r="AR13" s="53"/>
+      <c r="AO13" s="63"/>
+      <c r="AP13" s="63"/>
+      <c r="AQ13" s="66"/>
+      <c r="AR13" s="67"/>
     </row>
     <row r="14" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="33" t="s">
+      <c r="A14" s="97" t="s">
         <v>4</v>
       </c>
-      <c r="B14" s="31" t="s">
+      <c r="B14" s="100" t="s">
         <v>3</v>
       </c>
-      <c r="C14" s="31"/>
-      <c r="D14" s="32"/>
-      <c r="E14" s="113"/>
-      <c r="F14" s="113"/>
-      <c r="G14" s="113"/>
-      <c r="H14" s="113"/>
-      <c r="I14" s="113"/>
-      <c r="J14" s="113"/>
-      <c r="K14" s="113"/>
-      <c r="M14" s="40" t="s">
+      <c r="C14" s="100"/>
+      <c r="D14" s="101"/>
+      <c r="E14" s="119"/>
+      <c r="F14" s="119"/>
+      <c r="G14" s="119"/>
+      <c r="H14" s="119"/>
+      <c r="I14" s="119"/>
+      <c r="J14" s="119"/>
+      <c r="K14" s="119"/>
+      <c r="M14" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="N14" s="40"/>
-      <c r="O14" s="107"/>
-      <c r="P14" s="107"/>
-      <c r="Q14" s="107"/>
-      <c r="R14" s="107"/>
-      <c r="S14" s="107"/>
-      <c r="T14" s="107"/>
-      <c r="V14" s="37" t="s">
+      <c r="N14" s="61"/>
+      <c r="O14" s="29"/>
+      <c r="P14" s="29"/>
+      <c r="Q14" s="29"/>
+      <c r="R14" s="29"/>
+      <c r="S14" s="29"/>
+      <c r="T14" s="29"/>
+      <c r="V14" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="W14" s="37"/>
-      <c r="X14" s="107"/>
-      <c r="Y14" s="107"/>
-      <c r="Z14" s="107"/>
-      <c r="AA14" s="107"/>
-      <c r="AB14" s="107"/>
-      <c r="AC14" s="107"/>
+      <c r="W14" s="62"/>
+      <c r="X14" s="29"/>
+      <c r="Y14" s="29"/>
+      <c r="Z14" s="29"/>
+      <c r="AA14" s="29"/>
+      <c r="AB14" s="29"/>
+      <c r="AC14" s="29"/>
       <c r="AE14" s="7">
         <v>4</v>
       </c>
@@ -2434,50 +2434,50 @@
       </c>
       <c r="AH14" s="14"/>
       <c r="AI14" s="15"/>
-      <c r="AJ14" s="45" t="s">
+      <c r="AJ14" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="AK14" s="46"/>
+      <c r="AK14" s="52"/>
       <c r="AL14" s="14"/>
       <c r="AM14" s="15"/>
-      <c r="AN14" s="79"/>
+      <c r="AN14" s="87"/>
       <c r="AO14" s="64"/>
       <c r="AP14" s="64"/>
-      <c r="AQ14" s="54"/>
-      <c r="AR14" s="55"/>
+      <c r="AQ14" s="46"/>
+      <c r="AR14" s="47"/>
     </row>
     <row r="15" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="34"/>
-      <c r="B15" s="114"/>
-      <c r="C15" s="114"/>
-      <c r="D15" s="115"/>
-      <c r="E15" s="113"/>
-      <c r="F15" s="113"/>
-      <c r="G15" s="113"/>
-      <c r="H15" s="113"/>
-      <c r="I15" s="113"/>
-      <c r="J15" s="113"/>
-      <c r="K15" s="113"/>
-      <c r="M15" s="40" t="s">
+      <c r="A15" s="98"/>
+      <c r="B15" s="120"/>
+      <c r="C15" s="120"/>
+      <c r="D15" s="121"/>
+      <c r="E15" s="119"/>
+      <c r="F15" s="119"/>
+      <c r="G15" s="119"/>
+      <c r="H15" s="119"/>
+      <c r="I15" s="119"/>
+      <c r="J15" s="119"/>
+      <c r="K15" s="119"/>
+      <c r="M15" s="61" t="s">
         <v>5</v>
       </c>
-      <c r="N15" s="40"/>
-      <c r="O15" s="107"/>
-      <c r="P15" s="107"/>
-      <c r="Q15" s="107"/>
-      <c r="R15" s="107"/>
-      <c r="S15" s="107"/>
-      <c r="T15" s="107"/>
-      <c r="V15" s="37" t="s">
+      <c r="N15" s="61"/>
+      <c r="O15" s="29"/>
+      <c r="P15" s="29"/>
+      <c r="Q15" s="29"/>
+      <c r="R15" s="29"/>
+      <c r="S15" s="29"/>
+      <c r="T15" s="29"/>
+      <c r="V15" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="W15" s="37"/>
-      <c r="X15" s="107"/>
-      <c r="Y15" s="107"/>
-      <c r="Z15" s="107"/>
-      <c r="AA15" s="107"/>
-      <c r="AB15" s="107"/>
-      <c r="AC15" s="107"/>
+      <c r="W15" s="62"/>
+      <c r="X15" s="29"/>
+      <c r="Y15" s="29"/>
+      <c r="Z15" s="29"/>
+      <c r="AA15" s="29"/>
+      <c r="AB15" s="29"/>
+      <c r="AC15" s="29"/>
       <c r="AE15" s="7">
         <v>5</v>
       </c>
@@ -2487,82 +2487,82 @@
       <c r="AG15" s="17"/>
       <c r="AH15" s="14"/>
       <c r="AI15" s="15"/>
-      <c r="AJ15" s="45" t="s">
+      <c r="AJ15" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="AK15" s="46"/>
+      <c r="AK15" s="52"/>
       <c r="AL15" s="14"/>
       <c r="AM15" s="15"/>
-      <c r="AN15" s="80"/>
-      <c r="AO15" s="66" t="s">
+      <c r="AN15" s="53"/>
+      <c r="AO15" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="AP15" s="67"/>
-      <c r="AQ15" s="56"/>
-      <c r="AR15" s="57"/>
+      <c r="AP15" s="38"/>
+      <c r="AQ15" s="57"/>
+      <c r="AR15" s="58"/>
     </row>
     <row r="16" spans="1:44" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="34"/>
-      <c r="B16" s="114"/>
-      <c r="C16" s="114"/>
-      <c r="D16" s="115"/>
-      <c r="E16" s="113"/>
-      <c r="F16" s="113"/>
-      <c r="G16" s="113"/>
-      <c r="H16" s="113"/>
-      <c r="I16" s="113"/>
-      <c r="J16" s="113"/>
-      <c r="K16" s="113"/>
-      <c r="M16" s="40" t="s">
+      <c r="A16" s="98"/>
+      <c r="B16" s="120"/>
+      <c r="C16" s="120"/>
+      <c r="D16" s="121"/>
+      <c r="E16" s="119"/>
+      <c r="F16" s="119"/>
+      <c r="G16" s="119"/>
+      <c r="H16" s="119"/>
+      <c r="I16" s="119"/>
+      <c r="J16" s="119"/>
+      <c r="K16" s="119"/>
+      <c r="M16" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="N16" s="40"/>
-      <c r="O16" s="116"/>
-      <c r="P16" s="116"/>
-      <c r="Q16" s="107"/>
-      <c r="R16" s="107"/>
-      <c r="S16" s="107"/>
-      <c r="T16" s="107"/>
-      <c r="V16" s="37" t="s">
+      <c r="N16" s="61"/>
+      <c r="O16" s="30"/>
+      <c r="P16" s="30"/>
+      <c r="Q16" s="29"/>
+      <c r="R16" s="29"/>
+      <c r="S16" s="29"/>
+      <c r="T16" s="29"/>
+      <c r="V16" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="W16" s="37"/>
-      <c r="X16" s="107"/>
-      <c r="Y16" s="107"/>
-      <c r="Z16" s="107"/>
-      <c r="AA16" s="107"/>
-      <c r="AB16" s="107"/>
-      <c r="AC16" s="107"/>
+      <c r="W16" s="62"/>
+      <c r="X16" s="29"/>
+      <c r="Y16" s="29"/>
+      <c r="Z16" s="29"/>
+      <c r="AA16" s="29"/>
+      <c r="AB16" s="29"/>
+      <c r="AC16" s="29"/>
       <c r="AG16" s="17"/>
       <c r="AH16" s="14"/>
       <c r="AI16" s="15"/>
-      <c r="AJ16" s="45" t="s">
+      <c r="AJ16" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="AK16" s="46"/>
+      <c r="AK16" s="52"/>
       <c r="AL16" s="14"/>
       <c r="AM16" s="15"/>
-      <c r="AN16" s="81"/>
-      <c r="AO16" s="68"/>
-      <c r="AP16" s="69"/>
-      <c r="AQ16" s="58"/>
-      <c r="AR16" s="59"/>
+      <c r="AN16" s="54"/>
+      <c r="AO16" s="55"/>
+      <c r="AP16" s="56"/>
+      <c r="AQ16" s="59"/>
+      <c r="AR16" s="60"/>
     </row>
     <row r="17" spans="1:44" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="35"/>
-      <c r="B17" s="117"/>
-      <c r="C17" s="117"/>
-      <c r="D17" s="118"/>
-      <c r="E17" s="36" t="s">
+      <c r="A17" s="99"/>
+      <c r="B17" s="122"/>
+      <c r="C17" s="122"/>
+      <c r="D17" s="123"/>
+      <c r="E17" s="88" t="s">
         <v>11</v>
       </c>
-      <c r="F17" s="36"/>
-      <c r="G17" s="39"/>
-      <c r="H17" s="39"/>
-      <c r="I17" s="39"/>
-      <c r="J17" s="39"/>
-      <c r="K17" s="39"/>
-      <c r="L17" s="39"/>
+      <c r="F17" s="88"/>
+      <c r="G17" s="89"/>
+      <c r="H17" s="89"/>
+      <c r="I17" s="89"/>
+      <c r="J17" s="89"/>
+      <c r="K17" s="89"/>
+      <c r="L17" s="89"/>
       <c r="M17" s="18"/>
       <c r="N17" s="18"/>
       <c r="O17" s="18"/>
@@ -2586,64 +2586,64 @@
       <c r="AG17" s="20"/>
       <c r="AH17" s="21"/>
       <c r="AI17" s="22"/>
-      <c r="AJ17" s="70" t="s">
+      <c r="AJ17" s="90" t="s">
         <v>30</v>
       </c>
-      <c r="AK17" s="71"/>
+      <c r="AK17" s="91"/>
       <c r="AL17" s="21"/>
       <c r="AM17" s="22"/>
       <c r="AN17" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="AO17" s="60"/>
-      <c r="AP17" s="61"/>
-      <c r="AQ17" s="61"/>
-      <c r="AR17" s="62"/>
+      <c r="AO17" s="48"/>
+      <c r="AP17" s="49"/>
+      <c r="AQ17" s="49"/>
+      <c r="AR17" s="50"/>
     </row>
     <row r="18" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="102"/>
-      <c r="B18" s="103"/>
-      <c r="C18" s="103"/>
-      <c r="D18" s="104"/>
+      <c r="A18" s="128"/>
+      <c r="B18" s="112"/>
+      <c r="C18" s="112"/>
+      <c r="D18" s="113"/>
       <c r="E18" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F18" s="105"/>
-      <c r="G18" s="105"/>
-      <c r="H18" s="105"/>
-      <c r="I18" s="105"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="28"/>
+      <c r="I18" s="28"/>
       <c r="J18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K18" s="119"/>
-      <c r="L18" s="119"/>
-      <c r="M18" s="119"/>
-      <c r="N18" s="119"/>
-      <c r="O18" s="119"/>
-      <c r="P18" s="119"/>
-      <c r="Q18" s="119"/>
-      <c r="R18" s="119"/>
-      <c r="S18" s="119"/>
-      <c r="T18" s="119"/>
-      <c r="U18" s="119"/>
-      <c r="V18" s="119"/>
-      <c r="W18" s="119"/>
-      <c r="X18" s="47" t="s">
+      <c r="K18" s="133"/>
+      <c r="L18" s="133"/>
+      <c r="M18" s="133"/>
+      <c r="N18" s="133"/>
+      <c r="O18" s="133"/>
+      <c r="P18" s="133"/>
+      <c r="Q18" s="133"/>
+      <c r="R18" s="133"/>
+      <c r="S18" s="133"/>
+      <c r="T18" s="133"/>
+      <c r="U18" s="133"/>
+      <c r="V18" s="133"/>
+      <c r="W18" s="133"/>
+      <c r="X18" s="108" t="s">
         <v>15</v>
       </c>
-      <c r="Y18" s="47" t="s">
+      <c r="Y18" s="108" t="s">
         <v>16</v>
       </c>
-      <c r="Z18" s="47" t="s">
+      <c r="Z18" s="108" t="s">
         <v>17</v>
       </c>
-      <c r="AA18" s="47" t="s">
+      <c r="AA18" s="108" t="s">
         <v>18</v>
       </c>
-      <c r="AB18" s="47" t="s">
+      <c r="AB18" s="108" t="s">
         <v>0</v>
       </c>
-      <c r="AC18" s="47" t="s">
+      <c r="AC18" s="108" t="s">
         <v>19</v>
       </c>
       <c r="AD18" s="12"/>
@@ -2658,58 +2658,58 @@
       </c>
       <c r="AH18" s="14"/>
       <c r="AI18" s="15"/>
-      <c r="AJ18" s="45" t="s">
+      <c r="AJ18" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="AK18" s="46"/>
-      <c r="AL18" s="72"/>
-      <c r="AM18" s="73"/>
-      <c r="AN18" s="76" t="s">
+      <c r="AK18" s="52"/>
+      <c r="AL18" s="68"/>
+      <c r="AM18" s="69"/>
+      <c r="AN18" s="72" t="s">
         <v>31</v>
       </c>
-      <c r="AO18" s="63"/>
-      <c r="AP18" s="63"/>
-      <c r="AQ18" s="50"/>
-      <c r="AR18" s="51"/>
+      <c r="AO18" s="65"/>
+      <c r="AP18" s="65"/>
+      <c r="AQ18" s="44"/>
+      <c r="AR18" s="45"/>
     </row>
     <row r="19" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="30" t="s">
+      <c r="A19" s="115" t="s">
         <v>1</v>
       </c>
-      <c r="B19" s="28"/>
-      <c r="C19" s="28" t="s">
+      <c r="B19" s="116"/>
+      <c r="C19" s="116" t="s">
         <v>2</v>
       </c>
-      <c r="D19" s="29"/>
+      <c r="D19" s="117"/>
       <c r="E19" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F19" s="107"/>
-      <c r="G19" s="107"/>
-      <c r="H19" s="107"/>
-      <c r="I19" s="107"/>
+      <c r="F19" s="29"/>
+      <c r="G19" s="29"/>
+      <c r="H19" s="29"/>
+      <c r="I19" s="29"/>
       <c r="J19" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K19" s="120"/>
-      <c r="L19" s="120"/>
-      <c r="M19" s="120"/>
-      <c r="N19" s="120"/>
-      <c r="O19" s="120"/>
-      <c r="P19" s="120"/>
-      <c r="Q19" s="120"/>
-      <c r="R19" s="120"/>
-      <c r="S19" s="120"/>
-      <c r="T19" s="120"/>
-      <c r="U19" s="120"/>
-      <c r="V19" s="120"/>
-      <c r="W19" s="120"/>
-      <c r="X19" s="48"/>
-      <c r="Y19" s="48"/>
-      <c r="Z19" s="48"/>
-      <c r="AA19" s="48"/>
-      <c r="AB19" s="48"/>
-      <c r="AC19" s="48"/>
+      <c r="K19" s="134"/>
+      <c r="L19" s="134"/>
+      <c r="M19" s="134"/>
+      <c r="N19" s="134"/>
+      <c r="O19" s="134"/>
+      <c r="P19" s="134"/>
+      <c r="Q19" s="134"/>
+      <c r="R19" s="134"/>
+      <c r="S19" s="134"/>
+      <c r="T19" s="134"/>
+      <c r="U19" s="134"/>
+      <c r="V19" s="134"/>
+      <c r="W19" s="134"/>
+      <c r="X19" s="109"/>
+      <c r="Y19" s="109"/>
+      <c r="Z19" s="109"/>
+      <c r="AA19" s="109"/>
+      <c r="AB19" s="109"/>
+      <c r="AC19" s="109"/>
       <c r="AE19" s="7">
         <v>2</v>
       </c>
@@ -2721,35 +2721,35 @@
       </c>
       <c r="AH19" s="14"/>
       <c r="AI19" s="15"/>
-      <c r="AJ19" s="45" t="s">
+      <c r="AJ19" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="AK19" s="46"/>
-      <c r="AL19" s="74"/>
-      <c r="AM19" s="75"/>
-      <c r="AN19" s="77"/>
+      <c r="AK19" s="52"/>
+      <c r="AL19" s="70"/>
+      <c r="AM19" s="71"/>
+      <c r="AN19" s="73"/>
       <c r="AO19" s="64"/>
       <c r="AP19" s="64"/>
-      <c r="AQ19" s="52"/>
-      <c r="AR19" s="53"/>
+      <c r="AQ19" s="66"/>
+      <c r="AR19" s="67"/>
     </row>
     <row r="20" spans="1:44" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="109"/>
-      <c r="B20" s="110"/>
-      <c r="C20" s="111"/>
-      <c r="D20" s="112"/>
-      <c r="E20" s="38" t="s">
+      <c r="A20" s="124"/>
+      <c r="B20" s="125"/>
+      <c r="C20" s="126"/>
+      <c r="D20" s="127"/>
+      <c r="E20" s="107" t="s">
         <v>10</v>
       </c>
-      <c r="F20" s="38"/>
-      <c r="G20" s="38"/>
-      <c r="H20" s="38"/>
-      <c r="X20" s="49"/>
-      <c r="Y20" s="49"/>
-      <c r="Z20" s="49"/>
-      <c r="AA20" s="49"/>
-      <c r="AB20" s="49"/>
-      <c r="AC20" s="49"/>
+      <c r="F20" s="107"/>
+      <c r="G20" s="107"/>
+      <c r="H20" s="107"/>
+      <c r="X20" s="110"/>
+      <c r="Y20" s="110"/>
+      <c r="Z20" s="110"/>
+      <c r="AA20" s="110"/>
+      <c r="AB20" s="110"/>
+      <c r="AC20" s="110"/>
       <c r="AE20" s="7">
         <v>3</v>
       </c>
@@ -2761,56 +2761,56 @@
       </c>
       <c r="AH20" s="14"/>
       <c r="AI20" s="15"/>
-      <c r="AJ20" s="45" t="s">
+      <c r="AJ20" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="AK20" s="46"/>
+      <c r="AK20" s="52"/>
       <c r="AL20" s="14"/>
       <c r="AM20" s="15"/>
-      <c r="AN20" s="78" t="s">
+      <c r="AN20" s="86" t="s">
         <v>32</v>
       </c>
-      <c r="AO20" s="65"/>
-      <c r="AP20" s="65"/>
-      <c r="AQ20" s="52"/>
-      <c r="AR20" s="53"/>
+      <c r="AO20" s="63"/>
+      <c r="AP20" s="63"/>
+      <c r="AQ20" s="66"/>
+      <c r="AR20" s="67"/>
     </row>
     <row r="21" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="33" t="s">
+      <c r="A21" s="97" t="s">
         <v>4</v>
       </c>
-      <c r="B21" s="31" t="s">
+      <c r="B21" s="100" t="s">
         <v>3</v>
       </c>
-      <c r="C21" s="31"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="113"/>
-      <c r="F21" s="113"/>
-      <c r="G21" s="113"/>
-      <c r="H21" s="113"/>
-      <c r="I21" s="113"/>
-      <c r="J21" s="113"/>
-      <c r="K21" s="113"/>
-      <c r="M21" s="40" t="s">
+      <c r="C21" s="100"/>
+      <c r="D21" s="101"/>
+      <c r="E21" s="119"/>
+      <c r="F21" s="119"/>
+      <c r="G21" s="119"/>
+      <c r="H21" s="119"/>
+      <c r="I21" s="119"/>
+      <c r="J21" s="119"/>
+      <c r="K21" s="119"/>
+      <c r="M21" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="N21" s="40"/>
-      <c r="O21" s="107"/>
-      <c r="P21" s="107"/>
-      <c r="Q21" s="107"/>
-      <c r="R21" s="107"/>
-      <c r="S21" s="107"/>
-      <c r="T21" s="107"/>
-      <c r="V21" s="37" t="s">
+      <c r="N21" s="61"/>
+      <c r="O21" s="29"/>
+      <c r="P21" s="29"/>
+      <c r="Q21" s="29"/>
+      <c r="R21" s="29"/>
+      <c r="S21" s="29"/>
+      <c r="T21" s="29"/>
+      <c r="V21" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="W21" s="37"/>
-      <c r="X21" s="107"/>
-      <c r="Y21" s="107"/>
-      <c r="Z21" s="107"/>
-      <c r="AA21" s="107"/>
-      <c r="AB21" s="107"/>
-      <c r="AC21" s="107"/>
+      <c r="W21" s="62"/>
+      <c r="X21" s="29"/>
+      <c r="Y21" s="29"/>
+      <c r="Z21" s="29"/>
+      <c r="AA21" s="29"/>
+      <c r="AB21" s="29"/>
+      <c r="AC21" s="29"/>
       <c r="AE21" s="7">
         <v>4</v>
       </c>
@@ -2822,50 +2822,50 @@
       </c>
       <c r="AH21" s="14"/>
       <c r="AI21" s="15"/>
-      <c r="AJ21" s="45" t="s">
+      <c r="AJ21" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="AK21" s="46"/>
+      <c r="AK21" s="52"/>
       <c r="AL21" s="14"/>
       <c r="AM21" s="15"/>
-      <c r="AN21" s="79"/>
+      <c r="AN21" s="87"/>
       <c r="AO21" s="64"/>
       <c r="AP21" s="64"/>
-      <c r="AQ21" s="54"/>
-      <c r="AR21" s="55"/>
+      <c r="AQ21" s="46"/>
+      <c r="AR21" s="47"/>
     </row>
     <row r="22" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="34"/>
-      <c r="B22" s="114"/>
-      <c r="C22" s="114"/>
-      <c r="D22" s="115"/>
-      <c r="E22" s="113"/>
-      <c r="F22" s="113"/>
-      <c r="G22" s="113"/>
-      <c r="H22" s="113"/>
-      <c r="I22" s="113"/>
-      <c r="J22" s="113"/>
-      <c r="K22" s="113"/>
-      <c r="M22" s="40" t="s">
+      <c r="A22" s="98"/>
+      <c r="B22" s="120"/>
+      <c r="C22" s="120"/>
+      <c r="D22" s="121"/>
+      <c r="E22" s="119"/>
+      <c r="F22" s="119"/>
+      <c r="G22" s="119"/>
+      <c r="H22" s="119"/>
+      <c r="I22" s="119"/>
+      <c r="J22" s="119"/>
+      <c r="K22" s="119"/>
+      <c r="M22" s="61" t="s">
         <v>5</v>
       </c>
-      <c r="N22" s="40"/>
-      <c r="O22" s="107"/>
-      <c r="P22" s="107"/>
-      <c r="Q22" s="107"/>
-      <c r="R22" s="107"/>
-      <c r="S22" s="107"/>
-      <c r="T22" s="107"/>
-      <c r="V22" s="37" t="s">
+      <c r="N22" s="61"/>
+      <c r="O22" s="29"/>
+      <c r="P22" s="29"/>
+      <c r="Q22" s="29"/>
+      <c r="R22" s="29"/>
+      <c r="S22" s="29"/>
+      <c r="T22" s="29"/>
+      <c r="V22" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="W22" s="37"/>
-      <c r="X22" s="107"/>
-      <c r="Y22" s="107"/>
-      <c r="Z22" s="107"/>
-      <c r="AA22" s="107"/>
-      <c r="AB22" s="107"/>
-      <c r="AC22" s="107"/>
+      <c r="W22" s="62"/>
+      <c r="X22" s="29"/>
+      <c r="Y22" s="29"/>
+      <c r="Z22" s="29"/>
+      <c r="AA22" s="29"/>
+      <c r="AB22" s="29"/>
+      <c r="AC22" s="29"/>
       <c r="AE22" s="7">
         <v>5</v>
       </c>
@@ -2875,82 +2875,82 @@
       <c r="AG22" s="17"/>
       <c r="AH22" s="14"/>
       <c r="AI22" s="15"/>
-      <c r="AJ22" s="45" t="s">
+      <c r="AJ22" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="AK22" s="46"/>
+      <c r="AK22" s="52"/>
       <c r="AL22" s="14"/>
       <c r="AM22" s="15"/>
-      <c r="AN22" s="80"/>
-      <c r="AO22" s="66" t="s">
+      <c r="AN22" s="53"/>
+      <c r="AO22" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="AP22" s="67"/>
-      <c r="AQ22" s="56"/>
-      <c r="AR22" s="57"/>
+      <c r="AP22" s="38"/>
+      <c r="AQ22" s="57"/>
+      <c r="AR22" s="58"/>
     </row>
     <row r="23" spans="1:44" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="34"/>
-      <c r="B23" s="114"/>
-      <c r="C23" s="114"/>
-      <c r="D23" s="115"/>
-      <c r="E23" s="113"/>
-      <c r="F23" s="113"/>
-      <c r="G23" s="113"/>
-      <c r="H23" s="113"/>
-      <c r="I23" s="113"/>
-      <c r="J23" s="113"/>
-      <c r="K23" s="113"/>
-      <c r="M23" s="40" t="s">
+      <c r="A23" s="98"/>
+      <c r="B23" s="120"/>
+      <c r="C23" s="120"/>
+      <c r="D23" s="121"/>
+      <c r="E23" s="119"/>
+      <c r="F23" s="119"/>
+      <c r="G23" s="119"/>
+      <c r="H23" s="119"/>
+      <c r="I23" s="119"/>
+      <c r="J23" s="119"/>
+      <c r="K23" s="119"/>
+      <c r="M23" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="N23" s="40"/>
-      <c r="O23" s="121"/>
-      <c r="P23" s="121"/>
-      <c r="Q23" s="107"/>
-      <c r="R23" s="107"/>
-      <c r="S23" s="107"/>
-      <c r="T23" s="107"/>
-      <c r="V23" s="37" t="s">
+      <c r="N23" s="61"/>
+      <c r="O23" s="31"/>
+      <c r="P23" s="31"/>
+      <c r="Q23" s="29"/>
+      <c r="R23" s="29"/>
+      <c r="S23" s="29"/>
+      <c r="T23" s="29"/>
+      <c r="V23" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="W23" s="37"/>
-      <c r="X23" s="107"/>
-      <c r="Y23" s="107"/>
-      <c r="Z23" s="107"/>
-      <c r="AA23" s="107"/>
-      <c r="AB23" s="107"/>
-      <c r="AC23" s="107"/>
+      <c r="W23" s="62"/>
+      <c r="X23" s="29"/>
+      <c r="Y23" s="29"/>
+      <c r="Z23" s="29"/>
+      <c r="AA23" s="29"/>
+      <c r="AB23" s="29"/>
+      <c r="AC23" s="29"/>
       <c r="AG23" s="17"/>
       <c r="AH23" s="14"/>
       <c r="AI23" s="15"/>
-      <c r="AJ23" s="45" t="s">
+      <c r="AJ23" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="AK23" s="46"/>
+      <c r="AK23" s="52"/>
       <c r="AL23" s="14"/>
       <c r="AM23" s="15"/>
-      <c r="AN23" s="81"/>
-      <c r="AO23" s="68"/>
-      <c r="AP23" s="69"/>
-      <c r="AQ23" s="58"/>
-      <c r="AR23" s="59"/>
+      <c r="AN23" s="54"/>
+      <c r="AO23" s="55"/>
+      <c r="AP23" s="56"/>
+      <c r="AQ23" s="59"/>
+      <c r="AR23" s="60"/>
     </row>
     <row r="24" spans="1:44" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="35"/>
-      <c r="B24" s="117"/>
-      <c r="C24" s="117"/>
-      <c r="D24" s="118"/>
-      <c r="E24" s="36" t="s">
+      <c r="A24" s="99"/>
+      <c r="B24" s="122"/>
+      <c r="C24" s="122"/>
+      <c r="D24" s="123"/>
+      <c r="E24" s="88" t="s">
         <v>11</v>
       </c>
-      <c r="F24" s="36"/>
-      <c r="G24" s="39"/>
-      <c r="H24" s="39"/>
-      <c r="I24" s="39"/>
-      <c r="J24" s="39"/>
-      <c r="K24" s="39"/>
-      <c r="L24" s="39"/>
+      <c r="F24" s="88"/>
+      <c r="G24" s="89"/>
+      <c r="H24" s="89"/>
+      <c r="I24" s="89"/>
+      <c r="J24" s="89"/>
+      <c r="K24" s="89"/>
+      <c r="L24" s="89"/>
       <c r="M24" s="18"/>
       <c r="N24" s="18"/>
       <c r="O24" s="18"/>
@@ -2974,64 +2974,64 @@
       <c r="AG24" s="20"/>
       <c r="AH24" s="21"/>
       <c r="AI24" s="22"/>
-      <c r="AJ24" s="70" t="s">
+      <c r="AJ24" s="90" t="s">
         <v>30</v>
       </c>
-      <c r="AK24" s="71"/>
+      <c r="AK24" s="91"/>
       <c r="AL24" s="21"/>
       <c r="AM24" s="22"/>
       <c r="AN24" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="AO24" s="60"/>
-      <c r="AP24" s="61"/>
-      <c r="AQ24" s="61"/>
-      <c r="AR24" s="62"/>
+      <c r="AO24" s="48"/>
+      <c r="AP24" s="49"/>
+      <c r="AQ24" s="49"/>
+      <c r="AR24" s="50"/>
     </row>
     <row r="25" spans="1:44" x14ac:dyDescent="0.25">
-      <c r="A25" s="122"/>
-      <c r="B25" s="103"/>
-      <c r="C25" s="103"/>
-      <c r="D25" s="104"/>
+      <c r="A25" s="111"/>
+      <c r="B25" s="112"/>
+      <c r="C25" s="112"/>
+      <c r="D25" s="113"/>
       <c r="E25" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F25" s="123"/>
-      <c r="G25" s="123"/>
-      <c r="H25" s="123"/>
-      <c r="I25" s="123"/>
+      <c r="F25" s="32"/>
+      <c r="G25" s="32"/>
+      <c r="H25" s="32"/>
+      <c r="I25" s="32"/>
       <c r="J25" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K25" s="119"/>
-      <c r="L25" s="119"/>
-      <c r="M25" s="119"/>
-      <c r="N25" s="119"/>
-      <c r="O25" s="119"/>
-      <c r="P25" s="119"/>
-      <c r="Q25" s="119"/>
-      <c r="R25" s="119"/>
-      <c r="S25" s="119"/>
-      <c r="T25" s="119"/>
-      <c r="U25" s="119"/>
-      <c r="V25" s="119"/>
-      <c r="W25" s="119"/>
-      <c r="X25" s="47" t="s">
+      <c r="K25" s="114"/>
+      <c r="L25" s="114"/>
+      <c r="M25" s="114"/>
+      <c r="N25" s="114"/>
+      <c r="O25" s="114"/>
+      <c r="P25" s="114"/>
+      <c r="Q25" s="114"/>
+      <c r="R25" s="114"/>
+      <c r="S25" s="114"/>
+      <c r="T25" s="114"/>
+      <c r="U25" s="114"/>
+      <c r="V25" s="114"/>
+      <c r="W25" s="114"/>
+      <c r="X25" s="108" t="s">
         <v>15</v>
       </c>
-      <c r="Y25" s="47" t="s">
+      <c r="Y25" s="108" t="s">
         <v>16</v>
       </c>
-      <c r="Z25" s="47" t="s">
+      <c r="Z25" s="108" t="s">
         <v>17</v>
       </c>
-      <c r="AA25" s="47" t="s">
+      <c r="AA25" s="108" t="s">
         <v>18</v>
       </c>
-      <c r="AB25" s="47" t="s">
+      <c r="AB25" s="108" t="s">
         <v>0</v>
       </c>
-      <c r="AC25" s="47" t="s">
+      <c r="AC25" s="108" t="s">
         <v>19</v>
       </c>
       <c r="AD25" s="12"/>
@@ -3046,58 +3046,58 @@
       </c>
       <c r="AH25" s="14"/>
       <c r="AI25" s="15"/>
-      <c r="AJ25" s="45" t="s">
+      <c r="AJ25" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="AK25" s="46"/>
-      <c r="AL25" s="72"/>
-      <c r="AM25" s="73"/>
-      <c r="AN25" s="76" t="s">
+      <c r="AK25" s="52"/>
+      <c r="AL25" s="68"/>
+      <c r="AM25" s="69"/>
+      <c r="AN25" s="72" t="s">
         <v>31</v>
       </c>
-      <c r="AO25" s="63"/>
-      <c r="AP25" s="63"/>
-      <c r="AQ25" s="50"/>
-      <c r="AR25" s="51"/>
+      <c r="AO25" s="65"/>
+      <c r="AP25" s="65"/>
+      <c r="AQ25" s="44"/>
+      <c r="AR25" s="45"/>
     </row>
     <row r="26" spans="1:44" x14ac:dyDescent="0.25">
-      <c r="A26" s="30" t="s">
+      <c r="A26" s="115" t="s">
         <v>1</v>
       </c>
-      <c r="B26" s="28"/>
-      <c r="C26" s="28" t="s">
+      <c r="B26" s="116"/>
+      <c r="C26" s="116" t="s">
         <v>2</v>
       </c>
-      <c r="D26" s="29"/>
+      <c r="D26" s="117"/>
       <c r="E26" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F26" s="124"/>
-      <c r="G26" s="124"/>
-      <c r="H26" s="124"/>
-      <c r="I26" s="124"/>
+      <c r="F26" s="33"/>
+      <c r="G26" s="33"/>
+      <c r="H26" s="33"/>
+      <c r="I26" s="33"/>
       <c r="J26" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K26" s="120"/>
-      <c r="L26" s="120"/>
-      <c r="M26" s="120"/>
-      <c r="N26" s="120"/>
-      <c r="O26" s="120"/>
-      <c r="P26" s="120"/>
-      <c r="Q26" s="120"/>
-      <c r="R26" s="120"/>
-      <c r="S26" s="120"/>
-      <c r="T26" s="120"/>
-      <c r="U26" s="120"/>
-      <c r="V26" s="120"/>
-      <c r="W26" s="120"/>
-      <c r="X26" s="48"/>
-      <c r="Y26" s="48"/>
-      <c r="Z26" s="48"/>
-      <c r="AA26" s="48"/>
-      <c r="AB26" s="48"/>
-      <c r="AC26" s="48"/>
+      <c r="K26" s="118"/>
+      <c r="L26" s="118"/>
+      <c r="M26" s="118"/>
+      <c r="N26" s="118"/>
+      <c r="O26" s="118"/>
+      <c r="P26" s="118"/>
+      <c r="Q26" s="118"/>
+      <c r="R26" s="118"/>
+      <c r="S26" s="118"/>
+      <c r="T26" s="118"/>
+      <c r="U26" s="118"/>
+      <c r="V26" s="118"/>
+      <c r="W26" s="118"/>
+      <c r="X26" s="109"/>
+      <c r="Y26" s="109"/>
+      <c r="Z26" s="109"/>
+      <c r="AA26" s="109"/>
+      <c r="AB26" s="109"/>
+      <c r="AC26" s="109"/>
       <c r="AE26" s="7">
         <v>2</v>
       </c>
@@ -3109,35 +3109,35 @@
       </c>
       <c r="AH26" s="14"/>
       <c r="AI26" s="15"/>
-      <c r="AJ26" s="45" t="s">
+      <c r="AJ26" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="AK26" s="46"/>
-      <c r="AL26" s="74"/>
-      <c r="AM26" s="75"/>
-      <c r="AN26" s="77"/>
+      <c r="AK26" s="52"/>
+      <c r="AL26" s="70"/>
+      <c r="AM26" s="71"/>
+      <c r="AN26" s="73"/>
       <c r="AO26" s="64"/>
       <c r="AP26" s="64"/>
-      <c r="AQ26" s="52"/>
-      <c r="AR26" s="53"/>
+      <c r="AQ26" s="66"/>
+      <c r="AR26" s="67"/>
     </row>
     <row r="27" spans="1:44" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="125"/>
-      <c r="B27" s="126"/>
-      <c r="C27" s="127"/>
-      <c r="D27" s="128"/>
-      <c r="E27" s="38" t="s">
+      <c r="A27" s="103"/>
+      <c r="B27" s="104"/>
+      <c r="C27" s="105"/>
+      <c r="D27" s="106"/>
+      <c r="E27" s="107" t="s">
         <v>10</v>
       </c>
-      <c r="F27" s="38"/>
-      <c r="G27" s="38"/>
-      <c r="H27" s="38"/>
-      <c r="X27" s="49"/>
-      <c r="Y27" s="49"/>
-      <c r="Z27" s="49"/>
-      <c r="AA27" s="49"/>
-      <c r="AB27" s="49"/>
-      <c r="AC27" s="49"/>
+      <c r="F27" s="107"/>
+      <c r="G27" s="107"/>
+      <c r="H27" s="107"/>
+      <c r="X27" s="110"/>
+      <c r="Y27" s="110"/>
+      <c r="Z27" s="110"/>
+      <c r="AA27" s="110"/>
+      <c r="AB27" s="110"/>
+      <c r="AC27" s="110"/>
       <c r="AE27" s="7">
         <v>3</v>
       </c>
@@ -3149,56 +3149,56 @@
       </c>
       <c r="AH27" s="14"/>
       <c r="AI27" s="15"/>
-      <c r="AJ27" s="45" t="s">
+      <c r="AJ27" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="AK27" s="46"/>
+      <c r="AK27" s="52"/>
       <c r="AL27" s="14"/>
       <c r="AM27" s="15"/>
-      <c r="AN27" s="78" t="s">
+      <c r="AN27" s="86" t="s">
         <v>32</v>
       </c>
-      <c r="AO27" s="65"/>
-      <c r="AP27" s="65"/>
-      <c r="AQ27" s="52"/>
-      <c r="AR27" s="53"/>
+      <c r="AO27" s="63"/>
+      <c r="AP27" s="63"/>
+      <c r="AQ27" s="66"/>
+      <c r="AR27" s="67"/>
     </row>
     <row r="28" spans="1:44" x14ac:dyDescent="0.25">
-      <c r="A28" s="33" t="s">
+      <c r="A28" s="97" t="s">
         <v>4</v>
       </c>
-      <c r="B28" s="31" t="s">
+      <c r="B28" s="100" t="s">
         <v>3</v>
       </c>
-      <c r="C28" s="31"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="129"/>
-      <c r="F28" s="129"/>
-      <c r="G28" s="129"/>
-      <c r="H28" s="129"/>
-      <c r="I28" s="129"/>
-      <c r="J28" s="129"/>
-      <c r="K28" s="129"/>
-      <c r="M28" s="40" t="s">
+      <c r="C28" s="100"/>
+      <c r="D28" s="101"/>
+      <c r="E28" s="102"/>
+      <c r="F28" s="102"/>
+      <c r="G28" s="102"/>
+      <c r="H28" s="102"/>
+      <c r="I28" s="102"/>
+      <c r="J28" s="102"/>
+      <c r="K28" s="102"/>
+      <c r="M28" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="N28" s="40"/>
-      <c r="O28" s="130"/>
-      <c r="P28" s="130"/>
-      <c r="Q28" s="130"/>
-      <c r="R28" s="130"/>
-      <c r="S28" s="130"/>
-      <c r="T28" s="130"/>
-      <c r="V28" s="37" t="s">
+      <c r="N28" s="61"/>
+      <c r="O28" s="34"/>
+      <c r="P28" s="34"/>
+      <c r="Q28" s="34"/>
+      <c r="R28" s="34"/>
+      <c r="S28" s="34"/>
+      <c r="T28" s="34"/>
+      <c r="V28" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="W28" s="37"/>
-      <c r="X28" s="130"/>
-      <c r="Y28" s="130"/>
-      <c r="Z28" s="130"/>
-      <c r="AA28" s="130"/>
-      <c r="AB28" s="130"/>
-      <c r="AC28" s="130"/>
+      <c r="W28" s="62"/>
+      <c r="X28" s="34"/>
+      <c r="Y28" s="34"/>
+      <c r="Z28" s="34"/>
+      <c r="AA28" s="34"/>
+      <c r="AB28" s="34"/>
+      <c r="AC28" s="34"/>
       <c r="AE28" s="7">
         <v>4</v>
       </c>
@@ -3210,50 +3210,50 @@
       </c>
       <c r="AH28" s="14"/>
       <c r="AI28" s="15"/>
-      <c r="AJ28" s="45" t="s">
+      <c r="AJ28" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="AK28" s="46"/>
+      <c r="AK28" s="52"/>
       <c r="AL28" s="14"/>
       <c r="AM28" s="15"/>
-      <c r="AN28" s="79"/>
+      <c r="AN28" s="87"/>
       <c r="AO28" s="64"/>
       <c r="AP28" s="64"/>
-      <c r="AQ28" s="54"/>
-      <c r="AR28" s="55"/>
+      <c r="AQ28" s="46"/>
+      <c r="AR28" s="47"/>
     </row>
     <row r="29" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="34"/>
-      <c r="B29" s="131"/>
-      <c r="C29" s="131"/>
-      <c r="D29" s="132"/>
-      <c r="E29" s="129"/>
-      <c r="F29" s="129"/>
-      <c r="G29" s="129"/>
-      <c r="H29" s="129"/>
-      <c r="I29" s="129"/>
-      <c r="J29" s="129"/>
-      <c r="K29" s="129"/>
-      <c r="M29" s="40" t="s">
+      <c r="A29" s="98"/>
+      <c r="B29" s="74"/>
+      <c r="C29" s="74"/>
+      <c r="D29" s="75"/>
+      <c r="E29" s="102"/>
+      <c r="F29" s="102"/>
+      <c r="G29" s="102"/>
+      <c r="H29" s="102"/>
+      <c r="I29" s="102"/>
+      <c r="J29" s="102"/>
+      <c r="K29" s="102"/>
+      <c r="M29" s="61" t="s">
         <v>5</v>
       </c>
-      <c r="N29" s="40"/>
-      <c r="O29" s="130"/>
-      <c r="P29" s="130"/>
-      <c r="Q29" s="130"/>
-      <c r="R29" s="130"/>
-      <c r="S29" s="130"/>
-      <c r="T29" s="130"/>
-      <c r="V29" s="37" t="s">
+      <c r="N29" s="61"/>
+      <c r="O29" s="34"/>
+      <c r="P29" s="34"/>
+      <c r="Q29" s="34"/>
+      <c r="R29" s="34"/>
+      <c r="S29" s="34"/>
+      <c r="T29" s="34"/>
+      <c r="V29" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="W29" s="37"/>
-      <c r="X29" s="130"/>
-      <c r="Y29" s="130"/>
-      <c r="Z29" s="130"/>
-      <c r="AA29" s="130"/>
-      <c r="AB29" s="130"/>
-      <c r="AC29" s="130"/>
+      <c r="W29" s="62"/>
+      <c r="X29" s="34"/>
+      <c r="Y29" s="34"/>
+      <c r="Z29" s="34"/>
+      <c r="AA29" s="34"/>
+      <c r="AB29" s="34"/>
+      <c r="AC29" s="34"/>
       <c r="AE29" s="7">
         <v>5</v>
       </c>
@@ -3263,82 +3263,82 @@
       <c r="AG29" s="17"/>
       <c r="AH29" s="14"/>
       <c r="AI29" s="15"/>
-      <c r="AJ29" s="45" t="s">
+      <c r="AJ29" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="AK29" s="46"/>
+      <c r="AK29" s="52"/>
       <c r="AL29" s="14"/>
       <c r="AM29" s="15"/>
-      <c r="AN29" s="80"/>
-      <c r="AO29" s="66" t="s">
+      <c r="AN29" s="53"/>
+      <c r="AO29" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="AP29" s="67"/>
-      <c r="AQ29" s="56"/>
-      <c r="AR29" s="57"/>
+      <c r="AP29" s="38"/>
+      <c r="AQ29" s="57"/>
+      <c r="AR29" s="58"/>
     </row>
     <row r="30" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="34"/>
-      <c r="B30" s="131"/>
-      <c r="C30" s="131"/>
-      <c r="D30" s="132"/>
-      <c r="E30" s="129"/>
-      <c r="F30" s="129"/>
-      <c r="G30" s="129"/>
-      <c r="H30" s="129"/>
-      <c r="I30" s="129"/>
-      <c r="J30" s="129"/>
-      <c r="K30" s="129"/>
-      <c r="M30" s="40" t="s">
+      <c r="A30" s="98"/>
+      <c r="B30" s="74"/>
+      <c r="C30" s="74"/>
+      <c r="D30" s="75"/>
+      <c r="E30" s="102"/>
+      <c r="F30" s="102"/>
+      <c r="G30" s="102"/>
+      <c r="H30" s="102"/>
+      <c r="I30" s="102"/>
+      <c r="J30" s="102"/>
+      <c r="K30" s="102"/>
+      <c r="M30" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="N30" s="40"/>
-      <c r="O30" s="121"/>
-      <c r="P30" s="121"/>
-      <c r="Q30" s="130"/>
-      <c r="R30" s="130"/>
-      <c r="S30" s="130"/>
-      <c r="T30" s="130"/>
-      <c r="V30" s="37" t="s">
+      <c r="N30" s="61"/>
+      <c r="O30" s="31"/>
+      <c r="P30" s="31"/>
+      <c r="Q30" s="34"/>
+      <c r="R30" s="34"/>
+      <c r="S30" s="34"/>
+      <c r="T30" s="34"/>
+      <c r="V30" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="W30" s="37"/>
-      <c r="X30" s="130"/>
-      <c r="Y30" s="130"/>
-      <c r="Z30" s="130"/>
-      <c r="AA30" s="130"/>
-      <c r="AB30" s="130"/>
-      <c r="AC30" s="130"/>
+      <c r="W30" s="62"/>
+      <c r="X30" s="34"/>
+      <c r="Y30" s="34"/>
+      <c r="Z30" s="34"/>
+      <c r="AA30" s="34"/>
+      <c r="AB30" s="34"/>
+      <c r="AC30" s="34"/>
       <c r="AG30" s="17"/>
       <c r="AH30" s="14"/>
       <c r="AI30" s="15"/>
-      <c r="AJ30" s="45" t="s">
+      <c r="AJ30" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="AK30" s="46"/>
+      <c r="AK30" s="52"/>
       <c r="AL30" s="14"/>
       <c r="AM30" s="15"/>
-      <c r="AN30" s="81"/>
-      <c r="AO30" s="68"/>
-      <c r="AP30" s="69"/>
-      <c r="AQ30" s="58"/>
-      <c r="AR30" s="59"/>
+      <c r="AN30" s="54"/>
+      <c r="AO30" s="55"/>
+      <c r="AP30" s="56"/>
+      <c r="AQ30" s="59"/>
+      <c r="AR30" s="60"/>
     </row>
     <row r="31" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="35"/>
-      <c r="B31" s="133"/>
-      <c r="C31" s="133"/>
-      <c r="D31" s="134"/>
-      <c r="E31" s="36" t="s">
+      <c r="A31" s="99"/>
+      <c r="B31" s="76"/>
+      <c r="C31" s="76"/>
+      <c r="D31" s="77"/>
+      <c r="E31" s="88" t="s">
         <v>11</v>
       </c>
-      <c r="F31" s="36"/>
-      <c r="G31" s="39"/>
-      <c r="H31" s="39"/>
-      <c r="I31" s="39"/>
-      <c r="J31" s="39"/>
-      <c r="K31" s="39"/>
-      <c r="L31" s="39"/>
+      <c r="F31" s="88"/>
+      <c r="G31" s="89"/>
+      <c r="H31" s="89"/>
+      <c r="I31" s="89"/>
+      <c r="J31" s="89"/>
+      <c r="K31" s="89"/>
+      <c r="L31" s="89"/>
       <c r="M31" s="18"/>
       <c r="N31" s="18"/>
       <c r="O31" s="18"/>
@@ -3362,64 +3362,64 @@
       <c r="AG31" s="20"/>
       <c r="AH31" s="21"/>
       <c r="AI31" s="22"/>
-      <c r="AJ31" s="70" t="s">
+      <c r="AJ31" s="90" t="s">
         <v>30</v>
       </c>
-      <c r="AK31" s="71"/>
+      <c r="AK31" s="91"/>
       <c r="AL31" s="21"/>
       <c r="AM31" s="22"/>
       <c r="AN31" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="AO31" s="60"/>
-      <c r="AP31" s="61"/>
-      <c r="AQ31" s="61"/>
-      <c r="AR31" s="62"/>
+      <c r="AO31" s="48"/>
+      <c r="AP31" s="49"/>
+      <c r="AQ31" s="49"/>
+      <c r="AR31" s="50"/>
     </row>
     <row r="32" spans="1:44" x14ac:dyDescent="0.25">
-      <c r="A32" s="122"/>
-      <c r="B32" s="103"/>
-      <c r="C32" s="103"/>
-      <c r="D32" s="104"/>
+      <c r="A32" s="111"/>
+      <c r="B32" s="112"/>
+      <c r="C32" s="112"/>
+      <c r="D32" s="113"/>
       <c r="E32" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F32" s="123"/>
-      <c r="G32" s="123"/>
-      <c r="H32" s="123"/>
-      <c r="I32" s="123"/>
+      <c r="F32" s="32"/>
+      <c r="G32" s="32"/>
+      <c r="H32" s="32"/>
+      <c r="I32" s="32"/>
       <c r="J32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K32" s="119"/>
-      <c r="L32" s="119"/>
-      <c r="M32" s="119"/>
-      <c r="N32" s="119"/>
-      <c r="O32" s="119"/>
-      <c r="P32" s="119"/>
-      <c r="Q32" s="119"/>
-      <c r="R32" s="119"/>
-      <c r="S32" s="119"/>
-      <c r="T32" s="119"/>
-      <c r="U32" s="119"/>
-      <c r="V32" s="119"/>
-      <c r="W32" s="119"/>
-      <c r="X32" s="47" t="s">
+      <c r="K32" s="114"/>
+      <c r="L32" s="114"/>
+      <c r="M32" s="114"/>
+      <c r="N32" s="114"/>
+      <c r="O32" s="114"/>
+      <c r="P32" s="114"/>
+      <c r="Q32" s="114"/>
+      <c r="R32" s="114"/>
+      <c r="S32" s="114"/>
+      <c r="T32" s="114"/>
+      <c r="U32" s="114"/>
+      <c r="V32" s="114"/>
+      <c r="W32" s="114"/>
+      <c r="X32" s="108" t="s">
         <v>15</v>
       </c>
-      <c r="Y32" s="47" t="s">
+      <c r="Y32" s="108" t="s">
         <v>16</v>
       </c>
-      <c r="Z32" s="47" t="s">
+      <c r="Z32" s="108" t="s">
         <v>17</v>
       </c>
-      <c r="AA32" s="47" t="s">
+      <c r="AA32" s="108" t="s">
         <v>18</v>
       </c>
-      <c r="AB32" s="47" t="s">
+      <c r="AB32" s="108" t="s">
         <v>0</v>
       </c>
-      <c r="AC32" s="47" t="s">
+      <c r="AC32" s="108" t="s">
         <v>19</v>
       </c>
       <c r="AD32" s="12"/>
@@ -3434,58 +3434,58 @@
       </c>
       <c r="AH32" s="14"/>
       <c r="AI32" s="15"/>
-      <c r="AJ32" s="45" t="s">
+      <c r="AJ32" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="AK32" s="46"/>
-      <c r="AL32" s="72"/>
-      <c r="AM32" s="73"/>
-      <c r="AN32" s="76" t="s">
+      <c r="AK32" s="52"/>
+      <c r="AL32" s="68"/>
+      <c r="AM32" s="69"/>
+      <c r="AN32" s="72" t="s">
         <v>31</v>
       </c>
-      <c r="AO32" s="63"/>
-      <c r="AP32" s="63"/>
-      <c r="AQ32" s="50"/>
-      <c r="AR32" s="51"/>
+      <c r="AO32" s="65"/>
+      <c r="AP32" s="65"/>
+      <c r="AQ32" s="44"/>
+      <c r="AR32" s="45"/>
     </row>
     <row r="33" spans="1:44" x14ac:dyDescent="0.25">
-      <c r="A33" s="30" t="s">
+      <c r="A33" s="115" t="s">
         <v>1</v>
       </c>
-      <c r="B33" s="28"/>
-      <c r="C33" s="28" t="s">
+      <c r="B33" s="116"/>
+      <c r="C33" s="116" t="s">
         <v>2</v>
       </c>
-      <c r="D33" s="29"/>
+      <c r="D33" s="117"/>
       <c r="E33" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F33" s="124"/>
-      <c r="G33" s="124"/>
-      <c r="H33" s="124"/>
-      <c r="I33" s="124"/>
+      <c r="F33" s="33"/>
+      <c r="G33" s="33"/>
+      <c r="H33" s="33"/>
+      <c r="I33" s="33"/>
       <c r="J33" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K33" s="120"/>
-      <c r="L33" s="120"/>
-      <c r="M33" s="120"/>
-      <c r="N33" s="120"/>
-      <c r="O33" s="120"/>
-      <c r="P33" s="120"/>
-      <c r="Q33" s="120"/>
-      <c r="R33" s="120"/>
-      <c r="S33" s="120"/>
-      <c r="T33" s="120"/>
-      <c r="U33" s="120"/>
-      <c r="V33" s="120"/>
-      <c r="W33" s="120"/>
-      <c r="X33" s="48"/>
-      <c r="Y33" s="48"/>
-      <c r="Z33" s="48"/>
-      <c r="AA33" s="48"/>
-      <c r="AB33" s="48"/>
-      <c r="AC33" s="48"/>
+      <c r="K33" s="118"/>
+      <c r="L33" s="118"/>
+      <c r="M33" s="118"/>
+      <c r="N33" s="118"/>
+      <c r="O33" s="118"/>
+      <c r="P33" s="118"/>
+      <c r="Q33" s="118"/>
+      <c r="R33" s="118"/>
+      <c r="S33" s="118"/>
+      <c r="T33" s="118"/>
+      <c r="U33" s="118"/>
+      <c r="V33" s="118"/>
+      <c r="W33" s="118"/>
+      <c r="X33" s="109"/>
+      <c r="Y33" s="109"/>
+      <c r="Z33" s="109"/>
+      <c r="AA33" s="109"/>
+      <c r="AB33" s="109"/>
+      <c r="AC33" s="109"/>
       <c r="AE33" s="7">
         <v>2</v>
       </c>
@@ -3497,35 +3497,35 @@
       </c>
       <c r="AH33" s="14"/>
       <c r="AI33" s="15"/>
-      <c r="AJ33" s="45" t="s">
+      <c r="AJ33" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="AK33" s="46"/>
-      <c r="AL33" s="74"/>
-      <c r="AM33" s="75"/>
-      <c r="AN33" s="77"/>
+      <c r="AK33" s="52"/>
+      <c r="AL33" s="70"/>
+      <c r="AM33" s="71"/>
+      <c r="AN33" s="73"/>
       <c r="AO33" s="64"/>
       <c r="AP33" s="64"/>
-      <c r="AQ33" s="52"/>
-      <c r="AR33" s="53"/>
+      <c r="AQ33" s="66"/>
+      <c r="AR33" s="67"/>
     </row>
     <row r="34" spans="1:44" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="125"/>
-      <c r="B34" s="126"/>
-      <c r="C34" s="127"/>
-      <c r="D34" s="128"/>
-      <c r="E34" s="38" t="s">
+      <c r="A34" s="103"/>
+      <c r="B34" s="104"/>
+      <c r="C34" s="105"/>
+      <c r="D34" s="106"/>
+      <c r="E34" s="107" t="s">
         <v>10</v>
       </c>
-      <c r="F34" s="38"/>
-      <c r="G34" s="38"/>
-      <c r="H34" s="38"/>
-      <c r="X34" s="49"/>
-      <c r="Y34" s="49"/>
-      <c r="Z34" s="49"/>
-      <c r="AA34" s="49"/>
-      <c r="AB34" s="49"/>
-      <c r="AC34" s="49"/>
+      <c r="F34" s="107"/>
+      <c r="G34" s="107"/>
+      <c r="H34" s="107"/>
+      <c r="X34" s="110"/>
+      <c r="Y34" s="110"/>
+      <c r="Z34" s="110"/>
+      <c r="AA34" s="110"/>
+      <c r="AB34" s="110"/>
+      <c r="AC34" s="110"/>
       <c r="AE34" s="7">
         <v>3</v>
       </c>
@@ -3537,56 +3537,56 @@
       </c>
       <c r="AH34" s="14"/>
       <c r="AI34" s="15"/>
-      <c r="AJ34" s="45" t="s">
+      <c r="AJ34" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="AK34" s="46"/>
+      <c r="AK34" s="52"/>
       <c r="AL34" s="14"/>
       <c r="AM34" s="15"/>
-      <c r="AN34" s="78" t="s">
+      <c r="AN34" s="86" t="s">
         <v>32</v>
       </c>
-      <c r="AO34" s="65"/>
-      <c r="AP34" s="65"/>
-      <c r="AQ34" s="52"/>
-      <c r="AR34" s="53"/>
+      <c r="AO34" s="63"/>
+      <c r="AP34" s="63"/>
+      <c r="AQ34" s="66"/>
+      <c r="AR34" s="67"/>
     </row>
     <row r="35" spans="1:44" x14ac:dyDescent="0.25">
-      <c r="A35" s="33" t="s">
+      <c r="A35" s="97" t="s">
         <v>4</v>
       </c>
-      <c r="B35" s="31" t="s">
+      <c r="B35" s="100" t="s">
         <v>3</v>
       </c>
-      <c r="C35" s="31"/>
-      <c r="D35" s="32"/>
-      <c r="E35" s="129"/>
-      <c r="F35" s="129"/>
-      <c r="G35" s="129"/>
-      <c r="H35" s="129"/>
-      <c r="I35" s="129"/>
-      <c r="J35" s="129"/>
-      <c r="K35" s="129"/>
-      <c r="M35" s="40" t="s">
+      <c r="C35" s="100"/>
+      <c r="D35" s="101"/>
+      <c r="E35" s="102"/>
+      <c r="F35" s="102"/>
+      <c r="G35" s="102"/>
+      <c r="H35" s="102"/>
+      <c r="I35" s="102"/>
+      <c r="J35" s="102"/>
+      <c r="K35" s="102"/>
+      <c r="M35" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="N35" s="40"/>
-      <c r="O35" s="130"/>
-      <c r="P35" s="130"/>
-      <c r="Q35" s="130"/>
-      <c r="R35" s="130"/>
-      <c r="S35" s="130"/>
-      <c r="T35" s="130"/>
-      <c r="V35" s="37" t="s">
+      <c r="N35" s="61"/>
+      <c r="O35" s="34"/>
+      <c r="P35" s="34"/>
+      <c r="Q35" s="34"/>
+      <c r="R35" s="34"/>
+      <c r="S35" s="34"/>
+      <c r="T35" s="34"/>
+      <c r="V35" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="W35" s="37"/>
-      <c r="X35" s="130"/>
-      <c r="Y35" s="130"/>
-      <c r="Z35" s="130"/>
-      <c r="AA35" s="130"/>
-      <c r="AB35" s="130"/>
-      <c r="AC35" s="130"/>
+      <c r="W35" s="62"/>
+      <c r="X35" s="34"/>
+      <c r="Y35" s="34"/>
+      <c r="Z35" s="34"/>
+      <c r="AA35" s="34"/>
+      <c r="AB35" s="34"/>
+      <c r="AC35" s="34"/>
       <c r="AE35" s="7">
         <v>4</v>
       </c>
@@ -3598,50 +3598,50 @@
       </c>
       <c r="AH35" s="14"/>
       <c r="AI35" s="15"/>
-      <c r="AJ35" s="45" t="s">
+      <c r="AJ35" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="AK35" s="46"/>
+      <c r="AK35" s="52"/>
       <c r="AL35" s="14"/>
       <c r="AM35" s="15"/>
-      <c r="AN35" s="79"/>
+      <c r="AN35" s="87"/>
       <c r="AO35" s="64"/>
       <c r="AP35" s="64"/>
-      <c r="AQ35" s="54"/>
-      <c r="AR35" s="55"/>
+      <c r="AQ35" s="46"/>
+      <c r="AR35" s="47"/>
     </row>
     <row r="36" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="34"/>
-      <c r="B36" s="131"/>
-      <c r="C36" s="131"/>
-      <c r="D36" s="132"/>
-      <c r="E36" s="129"/>
-      <c r="F36" s="129"/>
-      <c r="G36" s="129"/>
-      <c r="H36" s="129"/>
-      <c r="I36" s="129"/>
-      <c r="J36" s="129"/>
-      <c r="K36" s="129"/>
-      <c r="M36" s="40" t="s">
+      <c r="A36" s="98"/>
+      <c r="B36" s="74"/>
+      <c r="C36" s="74"/>
+      <c r="D36" s="75"/>
+      <c r="E36" s="102"/>
+      <c r="F36" s="102"/>
+      <c r="G36" s="102"/>
+      <c r="H36" s="102"/>
+      <c r="I36" s="102"/>
+      <c r="J36" s="102"/>
+      <c r="K36" s="102"/>
+      <c r="M36" s="61" t="s">
         <v>5</v>
       </c>
-      <c r="N36" s="40"/>
-      <c r="O36" s="130"/>
-      <c r="P36" s="130"/>
-      <c r="Q36" s="130"/>
-      <c r="R36" s="130"/>
-      <c r="S36" s="130"/>
-      <c r="T36" s="130"/>
-      <c r="V36" s="37" t="s">
+      <c r="N36" s="61"/>
+      <c r="O36" s="34"/>
+      <c r="P36" s="34"/>
+      <c r="Q36" s="34"/>
+      <c r="R36" s="34"/>
+      <c r="S36" s="34"/>
+      <c r="T36" s="34"/>
+      <c r="V36" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="W36" s="37"/>
-      <c r="X36" s="130"/>
-      <c r="Y36" s="130"/>
-      <c r="Z36" s="130"/>
-      <c r="AA36" s="130"/>
-      <c r="AB36" s="130"/>
-      <c r="AC36" s="130"/>
+      <c r="W36" s="62"/>
+      <c r="X36" s="34"/>
+      <c r="Y36" s="34"/>
+      <c r="Z36" s="34"/>
+      <c r="AA36" s="34"/>
+      <c r="AB36" s="34"/>
+      <c r="AC36" s="34"/>
       <c r="AE36" s="7">
         <v>5</v>
       </c>
@@ -3651,82 +3651,82 @@
       <c r="AG36" s="17"/>
       <c r="AH36" s="14"/>
       <c r="AI36" s="15"/>
-      <c r="AJ36" s="45" t="s">
+      <c r="AJ36" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="AK36" s="46"/>
+      <c r="AK36" s="52"/>
       <c r="AL36" s="14"/>
       <c r="AM36" s="15"/>
-      <c r="AN36" s="80"/>
-      <c r="AO36" s="66" t="s">
+      <c r="AN36" s="53"/>
+      <c r="AO36" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="AP36" s="67"/>
-      <c r="AQ36" s="56"/>
-      <c r="AR36" s="57"/>
+      <c r="AP36" s="38"/>
+      <c r="AQ36" s="57"/>
+      <c r="AR36" s="58"/>
     </row>
     <row r="37" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="34"/>
-      <c r="B37" s="131"/>
-      <c r="C37" s="131"/>
-      <c r="D37" s="132"/>
-      <c r="E37" s="129"/>
-      <c r="F37" s="129"/>
-      <c r="G37" s="129"/>
-      <c r="H37" s="129"/>
-      <c r="I37" s="129"/>
-      <c r="J37" s="129"/>
-      <c r="K37" s="129"/>
-      <c r="M37" s="40" t="s">
+      <c r="A37" s="98"/>
+      <c r="B37" s="74"/>
+      <c r="C37" s="74"/>
+      <c r="D37" s="75"/>
+      <c r="E37" s="102"/>
+      <c r="F37" s="102"/>
+      <c r="G37" s="102"/>
+      <c r="H37" s="102"/>
+      <c r="I37" s="102"/>
+      <c r="J37" s="102"/>
+      <c r="K37" s="102"/>
+      <c r="M37" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="N37" s="40"/>
-      <c r="O37" s="121"/>
-      <c r="P37" s="121"/>
-      <c r="Q37" s="130"/>
-      <c r="R37" s="130"/>
-      <c r="S37" s="130"/>
-      <c r="T37" s="130"/>
-      <c r="V37" s="37" t="s">
+      <c r="N37" s="61"/>
+      <c r="O37" s="31"/>
+      <c r="P37" s="31"/>
+      <c r="Q37" s="34"/>
+      <c r="R37" s="34"/>
+      <c r="S37" s="34"/>
+      <c r="T37" s="34"/>
+      <c r="V37" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="W37" s="37"/>
-      <c r="X37" s="130"/>
-      <c r="Y37" s="130"/>
-      <c r="Z37" s="130"/>
-      <c r="AA37" s="130"/>
-      <c r="AB37" s="130"/>
-      <c r="AC37" s="130"/>
+      <c r="W37" s="62"/>
+      <c r="X37" s="34"/>
+      <c r="Y37" s="34"/>
+      <c r="Z37" s="34"/>
+      <c r="AA37" s="34"/>
+      <c r="AB37" s="34"/>
+      <c r="AC37" s="34"/>
       <c r="AG37" s="17"/>
       <c r="AH37" s="14"/>
       <c r="AI37" s="15"/>
-      <c r="AJ37" s="45" t="s">
+      <c r="AJ37" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="AK37" s="46"/>
+      <c r="AK37" s="52"/>
       <c r="AL37" s="14"/>
       <c r="AM37" s="15"/>
-      <c r="AN37" s="81"/>
-      <c r="AO37" s="68"/>
-      <c r="AP37" s="69"/>
-      <c r="AQ37" s="58"/>
-      <c r="AR37" s="59"/>
+      <c r="AN37" s="54"/>
+      <c r="AO37" s="55"/>
+      <c r="AP37" s="56"/>
+      <c r="AQ37" s="59"/>
+      <c r="AR37" s="60"/>
     </row>
     <row r="38" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="35"/>
-      <c r="B38" s="133"/>
-      <c r="C38" s="133"/>
-      <c r="D38" s="134"/>
-      <c r="E38" s="36" t="s">
+      <c r="A38" s="99"/>
+      <c r="B38" s="76"/>
+      <c r="C38" s="76"/>
+      <c r="D38" s="77"/>
+      <c r="E38" s="88" t="s">
         <v>11</v>
       </c>
-      <c r="F38" s="36"/>
-      <c r="G38" s="39"/>
-      <c r="H38" s="39"/>
-      <c r="I38" s="39"/>
-      <c r="J38" s="39"/>
-      <c r="K38" s="39"/>
-      <c r="L38" s="39"/>
+      <c r="F38" s="88"/>
+      <c r="G38" s="89"/>
+      <c r="H38" s="89"/>
+      <c r="I38" s="89"/>
+      <c r="J38" s="89"/>
+      <c r="K38" s="89"/>
+      <c r="L38" s="89"/>
       <c r="M38" s="18"/>
       <c r="N38" s="18"/>
       <c r="O38" s="18"/>
@@ -3750,64 +3750,64 @@
       <c r="AG38" s="20"/>
       <c r="AH38" s="21"/>
       <c r="AI38" s="22"/>
-      <c r="AJ38" s="70" t="s">
+      <c r="AJ38" s="90" t="s">
         <v>30</v>
       </c>
-      <c r="AK38" s="71"/>
+      <c r="AK38" s="91"/>
       <c r="AL38" s="21"/>
       <c r="AM38" s="22"/>
       <c r="AN38" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="AO38" s="60"/>
-      <c r="AP38" s="61"/>
-      <c r="AQ38" s="61"/>
-      <c r="AR38" s="62"/>
+      <c r="AO38" s="48"/>
+      <c r="AP38" s="49"/>
+      <c r="AQ38" s="49"/>
+      <c r="AR38" s="50"/>
     </row>
     <row r="39" spans="1:44" x14ac:dyDescent="0.25">
-      <c r="A39" s="122"/>
-      <c r="B39" s="103"/>
-      <c r="C39" s="103"/>
-      <c r="D39" s="104"/>
+      <c r="A39" s="111"/>
+      <c r="B39" s="112"/>
+      <c r="C39" s="112"/>
+      <c r="D39" s="113"/>
       <c r="E39" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F39" s="123"/>
-      <c r="G39" s="123"/>
-      <c r="H39" s="123"/>
-      <c r="I39" s="123"/>
+      <c r="F39" s="32"/>
+      <c r="G39" s="32"/>
+      <c r="H39" s="32"/>
+      <c r="I39" s="32"/>
       <c r="J39" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K39" s="119"/>
-      <c r="L39" s="119"/>
-      <c r="M39" s="119"/>
-      <c r="N39" s="119"/>
-      <c r="O39" s="119"/>
-      <c r="P39" s="119"/>
-      <c r="Q39" s="119"/>
-      <c r="R39" s="119"/>
-      <c r="S39" s="119"/>
-      <c r="T39" s="119"/>
-      <c r="U39" s="119"/>
-      <c r="V39" s="119"/>
-      <c r="W39" s="119"/>
-      <c r="X39" s="47" t="s">
+      <c r="K39" s="114"/>
+      <c r="L39" s="114"/>
+      <c r="M39" s="114"/>
+      <c r="N39" s="114"/>
+      <c r="O39" s="114"/>
+      <c r="P39" s="114"/>
+      <c r="Q39" s="114"/>
+      <c r="R39" s="114"/>
+      <c r="S39" s="114"/>
+      <c r="T39" s="114"/>
+      <c r="U39" s="114"/>
+      <c r="V39" s="114"/>
+      <c r="W39" s="114"/>
+      <c r="X39" s="108" t="s">
         <v>15</v>
       </c>
-      <c r="Y39" s="47" t="s">
+      <c r="Y39" s="108" t="s">
         <v>16</v>
       </c>
-      <c r="Z39" s="47" t="s">
+      <c r="Z39" s="108" t="s">
         <v>17</v>
       </c>
-      <c r="AA39" s="47" t="s">
+      <c r="AA39" s="108" t="s">
         <v>18</v>
       </c>
-      <c r="AB39" s="47" t="s">
+      <c r="AB39" s="108" t="s">
         <v>0</v>
       </c>
-      <c r="AC39" s="47" t="s">
+      <c r="AC39" s="108" t="s">
         <v>19</v>
       </c>
       <c r="AD39" s="12"/>
@@ -3822,58 +3822,58 @@
       </c>
       <c r="AH39" s="14"/>
       <c r="AI39" s="15"/>
-      <c r="AJ39" s="45" t="s">
+      <c r="AJ39" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="AK39" s="46"/>
-      <c r="AL39" s="72"/>
-      <c r="AM39" s="73"/>
-      <c r="AN39" s="76" t="s">
+      <c r="AK39" s="52"/>
+      <c r="AL39" s="68"/>
+      <c r="AM39" s="69"/>
+      <c r="AN39" s="72" t="s">
         <v>31</v>
       </c>
-      <c r="AO39" s="63"/>
-      <c r="AP39" s="63"/>
-      <c r="AQ39" s="50"/>
-      <c r="AR39" s="51"/>
+      <c r="AO39" s="65"/>
+      <c r="AP39" s="65"/>
+      <c r="AQ39" s="44"/>
+      <c r="AR39" s="45"/>
     </row>
     <row r="40" spans="1:44" x14ac:dyDescent="0.25">
-      <c r="A40" s="30" t="s">
+      <c r="A40" s="115" t="s">
         <v>1</v>
       </c>
-      <c r="B40" s="28"/>
-      <c r="C40" s="28" t="s">
+      <c r="B40" s="116"/>
+      <c r="C40" s="116" t="s">
         <v>2</v>
       </c>
-      <c r="D40" s="29"/>
+      <c r="D40" s="117"/>
       <c r="E40" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F40" s="124"/>
-      <c r="G40" s="124"/>
-      <c r="H40" s="124"/>
-      <c r="I40" s="124"/>
+      <c r="F40" s="33"/>
+      <c r="G40" s="33"/>
+      <c r="H40" s="33"/>
+      <c r="I40" s="33"/>
       <c r="J40" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K40" s="120"/>
-      <c r="L40" s="120"/>
-      <c r="M40" s="120"/>
-      <c r="N40" s="120"/>
-      <c r="O40" s="120"/>
-      <c r="P40" s="120"/>
-      <c r="Q40" s="120"/>
-      <c r="R40" s="120"/>
-      <c r="S40" s="120"/>
-      <c r="T40" s="120"/>
-      <c r="U40" s="120"/>
-      <c r="V40" s="120"/>
-      <c r="W40" s="120"/>
-      <c r="X40" s="48"/>
-      <c r="Y40" s="48"/>
-      <c r="Z40" s="48"/>
-      <c r="AA40" s="48"/>
-      <c r="AB40" s="48"/>
-      <c r="AC40" s="48"/>
+      <c r="K40" s="118"/>
+      <c r="L40" s="118"/>
+      <c r="M40" s="118"/>
+      <c r="N40" s="118"/>
+      <c r="O40" s="118"/>
+      <c r="P40" s="118"/>
+      <c r="Q40" s="118"/>
+      <c r="R40" s="118"/>
+      <c r="S40" s="118"/>
+      <c r="T40" s="118"/>
+      <c r="U40" s="118"/>
+      <c r="V40" s="118"/>
+      <c r="W40" s="118"/>
+      <c r="X40" s="109"/>
+      <c r="Y40" s="109"/>
+      <c r="Z40" s="109"/>
+      <c r="AA40" s="109"/>
+      <c r="AB40" s="109"/>
+      <c r="AC40" s="109"/>
       <c r="AE40" s="7">
         <v>2</v>
       </c>
@@ -3885,35 +3885,35 @@
       </c>
       <c r="AH40" s="14"/>
       <c r="AI40" s="15"/>
-      <c r="AJ40" s="45" t="s">
+      <c r="AJ40" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="AK40" s="46"/>
-      <c r="AL40" s="74"/>
-      <c r="AM40" s="75"/>
-      <c r="AN40" s="77"/>
+      <c r="AK40" s="52"/>
+      <c r="AL40" s="70"/>
+      <c r="AM40" s="71"/>
+      <c r="AN40" s="73"/>
       <c r="AO40" s="64"/>
       <c r="AP40" s="64"/>
-      <c r="AQ40" s="52"/>
-      <c r="AR40" s="53"/>
+      <c r="AQ40" s="66"/>
+      <c r="AR40" s="67"/>
     </row>
     <row r="41" spans="1:44" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="125"/>
-      <c r="B41" s="126"/>
-      <c r="C41" s="127"/>
-      <c r="D41" s="128"/>
-      <c r="E41" s="38" t="s">
+      <c r="A41" s="103"/>
+      <c r="B41" s="104"/>
+      <c r="C41" s="105"/>
+      <c r="D41" s="106"/>
+      <c r="E41" s="107" t="s">
         <v>10</v>
       </c>
-      <c r="F41" s="38"/>
-      <c r="G41" s="38"/>
-      <c r="H41" s="38"/>
-      <c r="X41" s="49"/>
-      <c r="Y41" s="49"/>
-      <c r="Z41" s="49"/>
-      <c r="AA41" s="49"/>
-      <c r="AB41" s="49"/>
-      <c r="AC41" s="49"/>
+      <c r="F41" s="107"/>
+      <c r="G41" s="107"/>
+      <c r="H41" s="107"/>
+      <c r="X41" s="110"/>
+      <c r="Y41" s="110"/>
+      <c r="Z41" s="110"/>
+      <c r="AA41" s="110"/>
+      <c r="AB41" s="110"/>
+      <c r="AC41" s="110"/>
       <c r="AE41" s="7">
         <v>3</v>
       </c>
@@ -3925,56 +3925,56 @@
       </c>
       <c r="AH41" s="14"/>
       <c r="AI41" s="15"/>
-      <c r="AJ41" s="45" t="s">
+      <c r="AJ41" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="AK41" s="46"/>
+      <c r="AK41" s="52"/>
       <c r="AL41" s="14"/>
       <c r="AM41" s="15"/>
-      <c r="AN41" s="78" t="s">
+      <c r="AN41" s="86" t="s">
         <v>32</v>
       </c>
-      <c r="AO41" s="65"/>
-      <c r="AP41" s="65"/>
-      <c r="AQ41" s="52"/>
-      <c r="AR41" s="53"/>
+      <c r="AO41" s="63"/>
+      <c r="AP41" s="63"/>
+      <c r="AQ41" s="66"/>
+      <c r="AR41" s="67"/>
     </row>
     <row r="42" spans="1:44" x14ac:dyDescent="0.25">
-      <c r="A42" s="33" t="s">
+      <c r="A42" s="97" t="s">
         <v>4</v>
       </c>
-      <c r="B42" s="31" t="s">
+      <c r="B42" s="100" t="s">
         <v>3</v>
       </c>
-      <c r="C42" s="31"/>
-      <c r="D42" s="32"/>
-      <c r="E42" s="129"/>
-      <c r="F42" s="129"/>
-      <c r="G42" s="129"/>
-      <c r="H42" s="129"/>
-      <c r="I42" s="129"/>
-      <c r="J42" s="129"/>
-      <c r="K42" s="129"/>
-      <c r="M42" s="40" t="s">
+      <c r="C42" s="100"/>
+      <c r="D42" s="101"/>
+      <c r="E42" s="102"/>
+      <c r="F42" s="102"/>
+      <c r="G42" s="102"/>
+      <c r="H42" s="102"/>
+      <c r="I42" s="102"/>
+      <c r="J42" s="102"/>
+      <c r="K42" s="102"/>
+      <c r="M42" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="N42" s="40"/>
-      <c r="O42" s="130"/>
-      <c r="P42" s="130"/>
-      <c r="Q42" s="130"/>
-      <c r="R42" s="130"/>
-      <c r="S42" s="130"/>
-      <c r="T42" s="130"/>
-      <c r="V42" s="37" t="s">
+      <c r="N42" s="61"/>
+      <c r="O42" s="34"/>
+      <c r="P42" s="34"/>
+      <c r="Q42" s="34"/>
+      <c r="R42" s="34"/>
+      <c r="S42" s="34"/>
+      <c r="T42" s="34"/>
+      <c r="V42" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="W42" s="37"/>
-      <c r="X42" s="130"/>
-      <c r="Y42" s="130"/>
-      <c r="Z42" s="130"/>
-      <c r="AA42" s="130"/>
-      <c r="AB42" s="130"/>
-      <c r="AC42" s="130"/>
+      <c r="W42" s="62"/>
+      <c r="X42" s="34"/>
+      <c r="Y42" s="34"/>
+      <c r="Z42" s="34"/>
+      <c r="AA42" s="34"/>
+      <c r="AB42" s="34"/>
+      <c r="AC42" s="34"/>
       <c r="AE42" s="7">
         <v>4</v>
       </c>
@@ -3986,50 +3986,50 @@
       </c>
       <c r="AH42" s="14"/>
       <c r="AI42" s="15"/>
-      <c r="AJ42" s="45" t="s">
+      <c r="AJ42" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="AK42" s="46"/>
+      <c r="AK42" s="52"/>
       <c r="AL42" s="14"/>
       <c r="AM42" s="15"/>
-      <c r="AN42" s="79"/>
+      <c r="AN42" s="87"/>
       <c r="AO42" s="64"/>
       <c r="AP42" s="64"/>
-      <c r="AQ42" s="54"/>
-      <c r="AR42" s="55"/>
+      <c r="AQ42" s="46"/>
+      <c r="AR42" s="47"/>
     </row>
     <row r="43" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="34"/>
-      <c r="B43" s="131"/>
-      <c r="C43" s="131"/>
-      <c r="D43" s="132"/>
-      <c r="E43" s="129"/>
-      <c r="F43" s="129"/>
-      <c r="G43" s="129"/>
-      <c r="H43" s="129"/>
-      <c r="I43" s="129"/>
-      <c r="J43" s="129"/>
-      <c r="K43" s="129"/>
-      <c r="M43" s="40" t="s">
+      <c r="A43" s="98"/>
+      <c r="B43" s="74"/>
+      <c r="C43" s="74"/>
+      <c r="D43" s="75"/>
+      <c r="E43" s="102"/>
+      <c r="F43" s="102"/>
+      <c r="G43" s="102"/>
+      <c r="H43" s="102"/>
+      <c r="I43" s="102"/>
+      <c r="J43" s="102"/>
+      <c r="K43" s="102"/>
+      <c r="M43" s="61" t="s">
         <v>5</v>
       </c>
-      <c r="N43" s="40"/>
-      <c r="O43" s="130"/>
-      <c r="P43" s="130"/>
-      <c r="Q43" s="130"/>
-      <c r="R43" s="130"/>
-      <c r="S43" s="130"/>
-      <c r="T43" s="130"/>
-      <c r="V43" s="37" t="s">
+      <c r="N43" s="61"/>
+      <c r="O43" s="34"/>
+      <c r="P43" s="34"/>
+      <c r="Q43" s="34"/>
+      <c r="R43" s="34"/>
+      <c r="S43" s="34"/>
+      <c r="T43" s="34"/>
+      <c r="V43" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="W43" s="37"/>
-      <c r="X43" s="130"/>
-      <c r="Y43" s="130"/>
-      <c r="Z43" s="130"/>
-      <c r="AA43" s="130"/>
-      <c r="AB43" s="130"/>
-      <c r="AC43" s="130"/>
+      <c r="W43" s="62"/>
+      <c r="X43" s="34"/>
+      <c r="Y43" s="34"/>
+      <c r="Z43" s="34"/>
+      <c r="AA43" s="34"/>
+      <c r="AB43" s="34"/>
+      <c r="AC43" s="34"/>
       <c r="AE43" s="7">
         <v>5</v>
       </c>
@@ -4039,82 +4039,82 @@
       <c r="AG43" s="17"/>
       <c r="AH43" s="14"/>
       <c r="AI43" s="15"/>
-      <c r="AJ43" s="45" t="s">
+      <c r="AJ43" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="AK43" s="46"/>
+      <c r="AK43" s="52"/>
       <c r="AL43" s="14"/>
       <c r="AM43" s="15"/>
-      <c r="AN43" s="80"/>
-      <c r="AO43" s="66" t="s">
+      <c r="AN43" s="53"/>
+      <c r="AO43" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="AP43" s="67"/>
-      <c r="AQ43" s="56"/>
-      <c r="AR43" s="57"/>
+      <c r="AP43" s="38"/>
+      <c r="AQ43" s="57"/>
+      <c r="AR43" s="58"/>
     </row>
     <row r="44" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="34"/>
-      <c r="B44" s="131"/>
-      <c r="C44" s="131"/>
-      <c r="D44" s="132"/>
-      <c r="E44" s="129"/>
-      <c r="F44" s="129"/>
-      <c r="G44" s="129"/>
-      <c r="H44" s="129"/>
-      <c r="I44" s="129"/>
-      <c r="J44" s="129"/>
-      <c r="K44" s="129"/>
-      <c r="M44" s="40" t="s">
+      <c r="A44" s="98"/>
+      <c r="B44" s="74"/>
+      <c r="C44" s="74"/>
+      <c r="D44" s="75"/>
+      <c r="E44" s="102"/>
+      <c r="F44" s="102"/>
+      <c r="G44" s="102"/>
+      <c r="H44" s="102"/>
+      <c r="I44" s="102"/>
+      <c r="J44" s="102"/>
+      <c r="K44" s="102"/>
+      <c r="M44" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="N44" s="40"/>
-      <c r="O44" s="121"/>
-      <c r="P44" s="121"/>
-      <c r="Q44" s="130"/>
-      <c r="R44" s="130"/>
-      <c r="S44" s="130"/>
-      <c r="T44" s="130"/>
-      <c r="V44" s="37" t="s">
+      <c r="N44" s="61"/>
+      <c r="O44" s="31"/>
+      <c r="P44" s="31"/>
+      <c r="Q44" s="34"/>
+      <c r="R44" s="34"/>
+      <c r="S44" s="34"/>
+      <c r="T44" s="34"/>
+      <c r="V44" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="W44" s="37"/>
-      <c r="X44" s="130"/>
-      <c r="Y44" s="130"/>
-      <c r="Z44" s="130"/>
-      <c r="AA44" s="130"/>
-      <c r="AB44" s="130"/>
-      <c r="AC44" s="130"/>
+      <c r="W44" s="62"/>
+      <c r="X44" s="34"/>
+      <c r="Y44" s="34"/>
+      <c r="Z44" s="34"/>
+      <c r="AA44" s="34"/>
+      <c r="AB44" s="34"/>
+      <c r="AC44" s="34"/>
       <c r="AG44" s="17"/>
       <c r="AH44" s="14"/>
       <c r="AI44" s="15"/>
-      <c r="AJ44" s="45" t="s">
+      <c r="AJ44" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="AK44" s="46"/>
+      <c r="AK44" s="52"/>
       <c r="AL44" s="14"/>
       <c r="AM44" s="15"/>
-      <c r="AN44" s="81"/>
-      <c r="AO44" s="68"/>
-      <c r="AP44" s="69"/>
-      <c r="AQ44" s="58"/>
-      <c r="AR44" s="59"/>
+      <c r="AN44" s="54"/>
+      <c r="AO44" s="55"/>
+      <c r="AP44" s="56"/>
+      <c r="AQ44" s="59"/>
+      <c r="AR44" s="60"/>
     </row>
     <row r="45" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="35"/>
-      <c r="B45" s="133"/>
-      <c r="C45" s="133"/>
-      <c r="D45" s="134"/>
-      <c r="E45" s="36" t="s">
+      <c r="A45" s="99"/>
+      <c r="B45" s="76"/>
+      <c r="C45" s="76"/>
+      <c r="D45" s="77"/>
+      <c r="E45" s="88" t="s">
         <v>11</v>
       </c>
-      <c r="F45" s="36"/>
-      <c r="G45" s="39"/>
-      <c r="H45" s="39"/>
-      <c r="I45" s="39"/>
-      <c r="J45" s="39"/>
-      <c r="K45" s="39"/>
-      <c r="L45" s="39"/>
+      <c r="F45" s="88"/>
+      <c r="G45" s="89"/>
+      <c r="H45" s="89"/>
+      <c r="I45" s="89"/>
+      <c r="J45" s="89"/>
+      <c r="K45" s="89"/>
+      <c r="L45" s="89"/>
       <c r="M45" s="18"/>
       <c r="N45" s="18"/>
       <c r="O45" s="18"/>
@@ -4138,64 +4138,64 @@
       <c r="AG45" s="20"/>
       <c r="AH45" s="21"/>
       <c r="AI45" s="22"/>
-      <c r="AJ45" s="70" t="s">
+      <c r="AJ45" s="90" t="s">
         <v>30</v>
       </c>
-      <c r="AK45" s="71"/>
+      <c r="AK45" s="91"/>
       <c r="AL45" s="21"/>
       <c r="AM45" s="22"/>
       <c r="AN45" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="AO45" s="60"/>
-      <c r="AP45" s="61"/>
-      <c r="AQ45" s="61"/>
-      <c r="AR45" s="62"/>
+      <c r="AO45" s="48"/>
+      <c r="AP45" s="49"/>
+      <c r="AQ45" s="49"/>
+      <c r="AR45" s="50"/>
     </row>
     <row r="46" spans="1:44" x14ac:dyDescent="0.25">
-      <c r="A46" s="122"/>
-      <c r="B46" s="103"/>
-      <c r="C46" s="103"/>
-      <c r="D46" s="104"/>
+      <c r="A46" s="111"/>
+      <c r="B46" s="112"/>
+      <c r="C46" s="112"/>
+      <c r="D46" s="113"/>
       <c r="E46" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F46" s="123"/>
-      <c r="G46" s="123"/>
-      <c r="H46" s="123"/>
-      <c r="I46" s="123"/>
+      <c r="F46" s="32"/>
+      <c r="G46" s="32"/>
+      <c r="H46" s="32"/>
+      <c r="I46" s="32"/>
       <c r="J46" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K46" s="119"/>
-      <c r="L46" s="119"/>
-      <c r="M46" s="119"/>
-      <c r="N46" s="119"/>
-      <c r="O46" s="119"/>
-      <c r="P46" s="119"/>
-      <c r="Q46" s="119"/>
-      <c r="R46" s="119"/>
-      <c r="S46" s="119"/>
-      <c r="T46" s="119"/>
-      <c r="U46" s="119"/>
-      <c r="V46" s="119"/>
-      <c r="W46" s="119"/>
-      <c r="X46" s="47" t="s">
+      <c r="K46" s="114"/>
+      <c r="L46" s="114"/>
+      <c r="M46" s="114"/>
+      <c r="N46" s="114"/>
+      <c r="O46" s="114"/>
+      <c r="P46" s="114"/>
+      <c r="Q46" s="114"/>
+      <c r="R46" s="114"/>
+      <c r="S46" s="114"/>
+      <c r="T46" s="114"/>
+      <c r="U46" s="114"/>
+      <c r="V46" s="114"/>
+      <c r="W46" s="114"/>
+      <c r="X46" s="108" t="s">
         <v>15</v>
       </c>
-      <c r="Y46" s="47" t="s">
+      <c r="Y46" s="108" t="s">
         <v>16</v>
       </c>
-      <c r="Z46" s="47" t="s">
+      <c r="Z46" s="108" t="s">
         <v>17</v>
       </c>
-      <c r="AA46" s="47" t="s">
+      <c r="AA46" s="108" t="s">
         <v>18</v>
       </c>
-      <c r="AB46" s="47" t="s">
+      <c r="AB46" s="108" t="s">
         <v>0</v>
       </c>
-      <c r="AC46" s="47" t="s">
+      <c r="AC46" s="108" t="s">
         <v>19</v>
       </c>
       <c r="AD46" s="12"/>
@@ -4210,58 +4210,58 @@
       </c>
       <c r="AH46" s="14"/>
       <c r="AI46" s="15"/>
-      <c r="AJ46" s="45" t="s">
+      <c r="AJ46" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="AK46" s="46"/>
-      <c r="AL46" s="72"/>
-      <c r="AM46" s="73"/>
-      <c r="AN46" s="76" t="s">
+      <c r="AK46" s="52"/>
+      <c r="AL46" s="68"/>
+      <c r="AM46" s="69"/>
+      <c r="AN46" s="72" t="s">
         <v>31</v>
       </c>
-      <c r="AO46" s="63"/>
-      <c r="AP46" s="63"/>
-      <c r="AQ46" s="50"/>
-      <c r="AR46" s="51"/>
+      <c r="AO46" s="65"/>
+      <c r="AP46" s="65"/>
+      <c r="AQ46" s="44"/>
+      <c r="AR46" s="45"/>
     </row>
     <row r="47" spans="1:44" x14ac:dyDescent="0.25">
-      <c r="A47" s="30" t="s">
+      <c r="A47" s="115" t="s">
         <v>1</v>
       </c>
-      <c r="B47" s="28"/>
-      <c r="C47" s="28" t="s">
+      <c r="B47" s="116"/>
+      <c r="C47" s="116" t="s">
         <v>2</v>
       </c>
-      <c r="D47" s="29"/>
+      <c r="D47" s="117"/>
       <c r="E47" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F47" s="124"/>
-      <c r="G47" s="124"/>
-      <c r="H47" s="124"/>
-      <c r="I47" s="124"/>
+      <c r="F47" s="33"/>
+      <c r="G47" s="33"/>
+      <c r="H47" s="33"/>
+      <c r="I47" s="33"/>
       <c r="J47" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K47" s="120"/>
-      <c r="L47" s="120"/>
-      <c r="M47" s="120"/>
-      <c r="N47" s="120"/>
-      <c r="O47" s="120"/>
-      <c r="P47" s="120"/>
-      <c r="Q47" s="120"/>
-      <c r="R47" s="120"/>
-      <c r="S47" s="120"/>
-      <c r="T47" s="120"/>
-      <c r="U47" s="120"/>
-      <c r="V47" s="120"/>
-      <c r="W47" s="120"/>
-      <c r="X47" s="48"/>
-      <c r="Y47" s="48"/>
-      <c r="Z47" s="48"/>
-      <c r="AA47" s="48"/>
-      <c r="AB47" s="48"/>
-      <c r="AC47" s="48"/>
+      <c r="K47" s="118"/>
+      <c r="L47" s="118"/>
+      <c r="M47" s="118"/>
+      <c r="N47" s="118"/>
+      <c r="O47" s="118"/>
+      <c r="P47" s="118"/>
+      <c r="Q47" s="118"/>
+      <c r="R47" s="118"/>
+      <c r="S47" s="118"/>
+      <c r="T47" s="118"/>
+      <c r="U47" s="118"/>
+      <c r="V47" s="118"/>
+      <c r="W47" s="118"/>
+      <c r="X47" s="109"/>
+      <c r="Y47" s="109"/>
+      <c r="Z47" s="109"/>
+      <c r="AA47" s="109"/>
+      <c r="AB47" s="109"/>
+      <c r="AC47" s="109"/>
       <c r="AE47" s="7">
         <v>2</v>
       </c>
@@ -4273,35 +4273,35 @@
       </c>
       <c r="AH47" s="14"/>
       <c r="AI47" s="15"/>
-      <c r="AJ47" s="45" t="s">
+      <c r="AJ47" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="AK47" s="46"/>
-      <c r="AL47" s="74"/>
-      <c r="AM47" s="75"/>
-      <c r="AN47" s="77"/>
+      <c r="AK47" s="52"/>
+      <c r="AL47" s="70"/>
+      <c r="AM47" s="71"/>
+      <c r="AN47" s="73"/>
       <c r="AO47" s="64"/>
       <c r="AP47" s="64"/>
-      <c r="AQ47" s="54"/>
-      <c r="AR47" s="55"/>
+      <c r="AQ47" s="46"/>
+      <c r="AR47" s="47"/>
     </row>
     <row r="48" spans="1:44" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="125"/>
-      <c r="B48" s="126"/>
-      <c r="C48" s="127"/>
-      <c r="D48" s="128"/>
-      <c r="E48" s="38" t="s">
+      <c r="A48" s="103"/>
+      <c r="B48" s="104"/>
+      <c r="C48" s="105"/>
+      <c r="D48" s="106"/>
+      <c r="E48" s="107" t="s">
         <v>10</v>
       </c>
-      <c r="F48" s="38"/>
-      <c r="G48" s="38"/>
-      <c r="H48" s="38"/>
-      <c r="X48" s="49"/>
-      <c r="Y48" s="49"/>
-      <c r="Z48" s="49"/>
-      <c r="AA48" s="49"/>
-      <c r="AB48" s="49"/>
-      <c r="AC48" s="49"/>
+      <c r="F48" s="107"/>
+      <c r="G48" s="107"/>
+      <c r="H48" s="107"/>
+      <c r="X48" s="110"/>
+      <c r="Y48" s="110"/>
+      <c r="Z48" s="110"/>
+      <c r="AA48" s="110"/>
+      <c r="AB48" s="110"/>
+      <c r="AC48" s="110"/>
       <c r="AE48" s="7">
         <v>3</v>
       </c>
@@ -4313,58 +4313,58 @@
       </c>
       <c r="AH48" s="14"/>
       <c r="AI48" s="15"/>
-      <c r="AJ48" s="45" t="s">
+      <c r="AJ48" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="AK48" s="46"/>
+      <c r="AK48" s="52"/>
       <c r="AL48" s="14"/>
       <c r="AM48" s="15"/>
-      <c r="AN48" s="78" t="s">
+      <c r="AN48" s="86" t="s">
         <v>32</v>
       </c>
-      <c r="AO48" s="66" t="s">
+      <c r="AO48" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="AP48" s="67"/>
-      <c r="AQ48" s="89"/>
-      <c r="AR48" s="91"/>
+      <c r="AP48" s="38"/>
+      <c r="AQ48" s="92"/>
+      <c r="AR48" s="94"/>
     </row>
     <row r="49" spans="1:44" x14ac:dyDescent="0.25">
-      <c r="A49" s="33" t="s">
+      <c r="A49" s="97" t="s">
         <v>4</v>
       </c>
-      <c r="B49" s="31" t="s">
+      <c r="B49" s="100" t="s">
         <v>3</v>
       </c>
-      <c r="C49" s="31"/>
-      <c r="D49" s="32"/>
-      <c r="E49" s="129"/>
-      <c r="F49" s="129"/>
-      <c r="G49" s="129"/>
-      <c r="H49" s="129"/>
-      <c r="I49" s="129"/>
-      <c r="J49" s="129"/>
-      <c r="K49" s="129"/>
-      <c r="M49" s="40" t="s">
+      <c r="C49" s="100"/>
+      <c r="D49" s="101"/>
+      <c r="E49" s="102"/>
+      <c r="F49" s="102"/>
+      <c r="G49" s="102"/>
+      <c r="H49" s="102"/>
+      <c r="I49" s="102"/>
+      <c r="J49" s="102"/>
+      <c r="K49" s="102"/>
+      <c r="M49" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="N49" s="40"/>
-      <c r="O49" s="130"/>
-      <c r="P49" s="130"/>
-      <c r="Q49" s="130"/>
-      <c r="R49" s="130"/>
-      <c r="S49" s="130"/>
-      <c r="T49" s="130"/>
-      <c r="V49" s="37" t="s">
+      <c r="N49" s="61"/>
+      <c r="O49" s="34"/>
+      <c r="P49" s="34"/>
+      <c r="Q49" s="34"/>
+      <c r="R49" s="34"/>
+      <c r="S49" s="34"/>
+      <c r="T49" s="34"/>
+      <c r="V49" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="W49" s="37"/>
-      <c r="X49" s="130"/>
-      <c r="Y49" s="130"/>
-      <c r="Z49" s="130"/>
-      <c r="AA49" s="130"/>
-      <c r="AB49" s="130"/>
-      <c r="AC49" s="130"/>
+      <c r="W49" s="62"/>
+      <c r="X49" s="34"/>
+      <c r="Y49" s="34"/>
+      <c r="Z49" s="34"/>
+      <c r="AA49" s="34"/>
+      <c r="AB49" s="34"/>
+      <c r="AC49" s="34"/>
       <c r="AE49" s="7">
         <v>4</v>
       </c>
@@ -4376,50 +4376,50 @@
       </c>
       <c r="AH49" s="14"/>
       <c r="AI49" s="15"/>
-      <c r="AJ49" s="45" t="s">
+      <c r="AJ49" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="AK49" s="46"/>
+      <c r="AK49" s="52"/>
       <c r="AL49" s="14"/>
       <c r="AM49" s="15"/>
-      <c r="AN49" s="79"/>
-      <c r="AO49" s="96"/>
-      <c r="AP49" s="97"/>
-      <c r="AQ49" s="90"/>
-      <c r="AR49" s="92"/>
+      <c r="AN49" s="87"/>
+      <c r="AO49" s="39"/>
+      <c r="AP49" s="40"/>
+      <c r="AQ49" s="93"/>
+      <c r="AR49" s="95"/>
     </row>
     <row r="50" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="34"/>
-      <c r="B50" s="131"/>
-      <c r="C50" s="131"/>
-      <c r="D50" s="132"/>
-      <c r="E50" s="129"/>
-      <c r="F50" s="129"/>
-      <c r="G50" s="129"/>
-      <c r="H50" s="129"/>
-      <c r="I50" s="129"/>
-      <c r="J50" s="129"/>
-      <c r="K50" s="129"/>
-      <c r="M50" s="40" t="s">
+      <c r="A50" s="98"/>
+      <c r="B50" s="74"/>
+      <c r="C50" s="74"/>
+      <c r="D50" s="75"/>
+      <c r="E50" s="102"/>
+      <c r="F50" s="102"/>
+      <c r="G50" s="102"/>
+      <c r="H50" s="102"/>
+      <c r="I50" s="102"/>
+      <c r="J50" s="102"/>
+      <c r="K50" s="102"/>
+      <c r="M50" s="61" t="s">
         <v>5</v>
       </c>
-      <c r="N50" s="40"/>
-      <c r="O50" s="130"/>
-      <c r="P50" s="130"/>
-      <c r="Q50" s="130"/>
-      <c r="R50" s="130"/>
-      <c r="S50" s="130"/>
-      <c r="T50" s="130"/>
-      <c r="V50" s="37" t="s">
+      <c r="N50" s="61"/>
+      <c r="O50" s="34"/>
+      <c r="P50" s="34"/>
+      <c r="Q50" s="34"/>
+      <c r="R50" s="34"/>
+      <c r="S50" s="34"/>
+      <c r="T50" s="34"/>
+      <c r="V50" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="W50" s="37"/>
-      <c r="X50" s="130"/>
-      <c r="Y50" s="130"/>
-      <c r="Z50" s="130"/>
-      <c r="AA50" s="130"/>
-      <c r="AB50" s="130"/>
-      <c r="AC50" s="130"/>
+      <c r="W50" s="62"/>
+      <c r="X50" s="34"/>
+      <c r="Y50" s="34"/>
+      <c r="Z50" s="34"/>
+      <c r="AA50" s="34"/>
+      <c r="AB50" s="34"/>
+      <c r="AC50" s="34"/>
       <c r="AE50" s="7">
         <v>5</v>
       </c>
@@ -4429,82 +4429,82 @@
       <c r="AG50" s="17"/>
       <c r="AH50" s="14"/>
       <c r="AI50" s="15"/>
-      <c r="AJ50" s="45" t="s">
+      <c r="AJ50" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="AK50" s="46"/>
+      <c r="AK50" s="52"/>
       <c r="AL50" s="14"/>
       <c r="AM50" s="15"/>
-      <c r="AN50" s="80"/>
-      <c r="AO50" s="85" t="s">
+      <c r="AN50" s="53"/>
+      <c r="AO50" s="82" t="s">
         <v>42</v>
       </c>
-      <c r="AP50" s="86"/>
-      <c r="AQ50" s="93"/>
-      <c r="AR50" s="94"/>
+      <c r="AP50" s="83"/>
+      <c r="AQ50" s="96"/>
+      <c r="AR50" s="35"/>
     </row>
     <row r="51" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="34"/>
-      <c r="B51" s="131"/>
-      <c r="C51" s="131"/>
-      <c r="D51" s="132"/>
-      <c r="E51" s="129"/>
-      <c r="F51" s="129"/>
-      <c r="G51" s="129"/>
-      <c r="H51" s="129"/>
-      <c r="I51" s="129"/>
-      <c r="J51" s="129"/>
-      <c r="K51" s="129"/>
-      <c r="M51" s="40" t="s">
+      <c r="A51" s="98"/>
+      <c r="B51" s="74"/>
+      <c r="C51" s="74"/>
+      <c r="D51" s="75"/>
+      <c r="E51" s="102"/>
+      <c r="F51" s="102"/>
+      <c r="G51" s="102"/>
+      <c r="H51" s="102"/>
+      <c r="I51" s="102"/>
+      <c r="J51" s="102"/>
+      <c r="K51" s="102"/>
+      <c r="M51" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="N51" s="40"/>
-      <c r="O51" s="121"/>
-      <c r="P51" s="121"/>
-      <c r="Q51" s="130"/>
-      <c r="R51" s="130"/>
-      <c r="S51" s="130"/>
-      <c r="T51" s="130"/>
-      <c r="V51" s="37" t="s">
+      <c r="N51" s="61"/>
+      <c r="O51" s="31"/>
+      <c r="P51" s="31"/>
+      <c r="Q51" s="34"/>
+      <c r="R51" s="34"/>
+      <c r="S51" s="34"/>
+      <c r="T51" s="34"/>
+      <c r="V51" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="W51" s="37"/>
-      <c r="X51" s="130"/>
-      <c r="Y51" s="130"/>
-      <c r="Z51" s="130"/>
-      <c r="AA51" s="130"/>
-      <c r="AB51" s="130"/>
-      <c r="AC51" s="130"/>
+      <c r="W51" s="62"/>
+      <c r="X51" s="34"/>
+      <c r="Y51" s="34"/>
+      <c r="Z51" s="34"/>
+      <c r="AA51" s="34"/>
+      <c r="AB51" s="34"/>
+      <c r="AC51" s="34"/>
       <c r="AG51" s="17"/>
       <c r="AH51" s="14"/>
       <c r="AI51" s="15"/>
-      <c r="AJ51" s="45" t="s">
+      <c r="AJ51" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="AK51" s="46"/>
+      <c r="AK51" s="52"/>
       <c r="AL51" s="14"/>
       <c r="AM51" s="15"/>
-      <c r="AN51" s="81"/>
-      <c r="AO51" s="87"/>
-      <c r="AP51" s="88"/>
-      <c r="AQ51" s="60"/>
-      <c r="AR51" s="95"/>
+      <c r="AN51" s="54"/>
+      <c r="AO51" s="84"/>
+      <c r="AP51" s="85"/>
+      <c r="AQ51" s="48"/>
+      <c r="AR51" s="36"/>
     </row>
     <row r="52" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="35"/>
-      <c r="B52" s="133"/>
-      <c r="C52" s="133"/>
-      <c r="D52" s="134"/>
-      <c r="E52" s="36" t="s">
+      <c r="A52" s="99"/>
+      <c r="B52" s="76"/>
+      <c r="C52" s="76"/>
+      <c r="D52" s="77"/>
+      <c r="E52" s="88" t="s">
         <v>11</v>
       </c>
-      <c r="F52" s="36"/>
-      <c r="G52" s="39"/>
-      <c r="H52" s="39"/>
-      <c r="I52" s="39"/>
-      <c r="J52" s="39"/>
-      <c r="K52" s="39"/>
-      <c r="L52" s="39"/>
+      <c r="F52" s="88"/>
+      <c r="G52" s="89"/>
+      <c r="H52" s="89"/>
+      <c r="I52" s="89"/>
+      <c r="J52" s="89"/>
+      <c r="K52" s="89"/>
+      <c r="L52" s="89"/>
       <c r="M52" s="18"/>
       <c r="N52" s="18"/>
       <c r="O52" s="18"/>
@@ -4528,22 +4528,329 @@
       <c r="AG52" s="20"/>
       <c r="AH52" s="21"/>
       <c r="AI52" s="22"/>
-      <c r="AJ52" s="70" t="s">
+      <c r="AJ52" s="90" t="s">
         <v>30</v>
       </c>
-      <c r="AK52" s="71"/>
+      <c r="AK52" s="91"/>
       <c r="AL52" s="21"/>
       <c r="AM52" s="22"/>
       <c r="AN52" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="AO52" s="60"/>
-      <c r="AP52" s="61"/>
-      <c r="AQ52" s="61"/>
-      <c r="AR52" s="62"/>
+      <c r="AO52" s="48"/>
+      <c r="AP52" s="49"/>
+      <c r="AQ52" s="49"/>
+      <c r="AR52" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="331">
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="A7:A10"/>
+    <mergeCell ref="B8:D10"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="V7:W7"/>
+    <mergeCell ref="V8:W8"/>
+    <mergeCell ref="V9:W9"/>
+    <mergeCell ref="E6:H6"/>
+    <mergeCell ref="E7:K9"/>
+    <mergeCell ref="G10:L10"/>
+    <mergeCell ref="K4:W4"/>
+    <mergeCell ref="K5:W5"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="M9:N9"/>
+    <mergeCell ref="AH3:AI3"/>
+    <mergeCell ref="AJ3:AK3"/>
+    <mergeCell ref="AL3:AM3"/>
+    <mergeCell ref="AJ4:AK4"/>
+    <mergeCell ref="AJ5:AK5"/>
+    <mergeCell ref="AJ6:AK6"/>
+    <mergeCell ref="X4:X6"/>
+    <mergeCell ref="Y4:Y6"/>
+    <mergeCell ref="Z4:Z6"/>
+    <mergeCell ref="AA4:AA6"/>
+    <mergeCell ref="AB4:AB6"/>
+    <mergeCell ref="AC4:AC6"/>
+    <mergeCell ref="AQ4:AR7"/>
+    <mergeCell ref="AQ8:AR9"/>
+    <mergeCell ref="AO10:AR10"/>
+    <mergeCell ref="AO4:AO5"/>
+    <mergeCell ref="AP4:AP5"/>
+    <mergeCell ref="AO6:AO7"/>
+    <mergeCell ref="AP6:AP7"/>
+    <mergeCell ref="AO8:AP9"/>
+    <mergeCell ref="AJ7:AK7"/>
+    <mergeCell ref="AJ8:AK8"/>
+    <mergeCell ref="AJ9:AK9"/>
+    <mergeCell ref="AJ10:AK10"/>
+    <mergeCell ref="AL4:AM5"/>
+    <mergeCell ref="AN4:AN5"/>
+    <mergeCell ref="AN6:AN7"/>
+    <mergeCell ref="AN8:AN9"/>
+    <mergeCell ref="AP11:AP12"/>
+    <mergeCell ref="AQ11:AR14"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="K12:W12"/>
+    <mergeCell ref="AJ12:AK12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="E13:H13"/>
+    <mergeCell ref="AJ13:AK13"/>
+    <mergeCell ref="AB11:AB13"/>
+    <mergeCell ref="AC11:AC13"/>
+    <mergeCell ref="AJ11:AK11"/>
+    <mergeCell ref="AL11:AM12"/>
+    <mergeCell ref="AN11:AN12"/>
+    <mergeCell ref="AO11:AO12"/>
+    <mergeCell ref="AN13:AN14"/>
+    <mergeCell ref="AO13:AO14"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="K11:W11"/>
+    <mergeCell ref="X11:X13"/>
+    <mergeCell ref="Y11:Y13"/>
+    <mergeCell ref="Z11:Z13"/>
+    <mergeCell ref="AA11:AA13"/>
+    <mergeCell ref="AP13:AP14"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="E14:K16"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="V14:W14"/>
+    <mergeCell ref="AJ14:AK14"/>
+    <mergeCell ref="B15:D17"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="V15:W15"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:L17"/>
+    <mergeCell ref="AJ17:AK17"/>
+    <mergeCell ref="AO17:AR17"/>
+    <mergeCell ref="AJ15:AK15"/>
+    <mergeCell ref="AN15:AN16"/>
+    <mergeCell ref="AO15:AP16"/>
+    <mergeCell ref="AQ15:AR16"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="V16:W16"/>
+    <mergeCell ref="AJ16:AK16"/>
+    <mergeCell ref="AP18:AP19"/>
+    <mergeCell ref="AQ18:AR21"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="K19:W19"/>
+    <mergeCell ref="AJ19:AK19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:H20"/>
+    <mergeCell ref="AJ20:AK20"/>
+    <mergeCell ref="AB18:AB20"/>
+    <mergeCell ref="AC18:AC20"/>
+    <mergeCell ref="AJ18:AK18"/>
+    <mergeCell ref="AL18:AM19"/>
+    <mergeCell ref="AN18:AN19"/>
+    <mergeCell ref="AO18:AO19"/>
+    <mergeCell ref="AN20:AN21"/>
+    <mergeCell ref="AO20:AO21"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="K18:W18"/>
+    <mergeCell ref="X18:X20"/>
+    <mergeCell ref="Y18:Y20"/>
+    <mergeCell ref="Z18:Z20"/>
+    <mergeCell ref="AA18:AA20"/>
+    <mergeCell ref="AP20:AP21"/>
+    <mergeCell ref="A21:A24"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="E21:K23"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="V21:W21"/>
+    <mergeCell ref="AJ21:AK21"/>
+    <mergeCell ref="B22:D24"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="V22:W22"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="G24:L24"/>
+    <mergeCell ref="AJ24:AK24"/>
+    <mergeCell ref="AO24:AR24"/>
+    <mergeCell ref="AJ22:AK22"/>
+    <mergeCell ref="AN22:AN23"/>
+    <mergeCell ref="AO22:AP23"/>
+    <mergeCell ref="AQ22:AR23"/>
+    <mergeCell ref="M23:N23"/>
+    <mergeCell ref="V23:W23"/>
+    <mergeCell ref="AJ23:AK23"/>
+    <mergeCell ref="AP25:AP26"/>
+    <mergeCell ref="AQ25:AR28"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="K26:W26"/>
+    <mergeCell ref="AJ26:AK26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:H27"/>
+    <mergeCell ref="AJ27:AK27"/>
+    <mergeCell ref="AB25:AB27"/>
+    <mergeCell ref="AC25:AC27"/>
+    <mergeCell ref="AJ25:AK25"/>
+    <mergeCell ref="AL25:AM26"/>
+    <mergeCell ref="AN25:AN26"/>
+    <mergeCell ref="AO25:AO26"/>
+    <mergeCell ref="AN27:AN28"/>
+    <mergeCell ref="AO27:AO28"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="K25:W25"/>
+    <mergeCell ref="X25:X27"/>
+    <mergeCell ref="Y25:Y27"/>
+    <mergeCell ref="Z25:Z27"/>
+    <mergeCell ref="AA25:AA27"/>
+    <mergeCell ref="Y32:Y34"/>
+    <mergeCell ref="Z32:Z34"/>
+    <mergeCell ref="AA32:AA34"/>
+    <mergeCell ref="AP27:AP28"/>
+    <mergeCell ref="A28:A31"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="E28:K30"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="V28:W28"/>
+    <mergeCell ref="AJ28:AK28"/>
+    <mergeCell ref="B29:D31"/>
+    <mergeCell ref="M29:N29"/>
+    <mergeCell ref="V29:W29"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="G31:L31"/>
+    <mergeCell ref="AJ31:AK31"/>
+    <mergeCell ref="AO31:AR31"/>
+    <mergeCell ref="AJ29:AK29"/>
+    <mergeCell ref="AN29:AN30"/>
+    <mergeCell ref="AO29:AP30"/>
+    <mergeCell ref="AQ29:AR30"/>
+    <mergeCell ref="M30:N30"/>
+    <mergeCell ref="V30:W30"/>
+    <mergeCell ref="AJ30:AK30"/>
+    <mergeCell ref="M37:N37"/>
+    <mergeCell ref="V37:W37"/>
+    <mergeCell ref="AJ37:AK37"/>
+    <mergeCell ref="AP32:AP33"/>
+    <mergeCell ref="AQ32:AR35"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="K33:W33"/>
+    <mergeCell ref="AJ33:AK33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="E34:H34"/>
+    <mergeCell ref="AJ34:AK34"/>
+    <mergeCell ref="AB32:AB34"/>
+    <mergeCell ref="AC32:AC34"/>
+    <mergeCell ref="AJ32:AK32"/>
+    <mergeCell ref="AL32:AM33"/>
+    <mergeCell ref="AN32:AN33"/>
+    <mergeCell ref="AO32:AO33"/>
+    <mergeCell ref="AN34:AN35"/>
+    <mergeCell ref="AO34:AO35"/>
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="K32:W32"/>
+    <mergeCell ref="X32:X34"/>
+    <mergeCell ref="AC39:AC41"/>
+    <mergeCell ref="AJ39:AK39"/>
+    <mergeCell ref="A42:A45"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="E42:K44"/>
+    <mergeCell ref="M42:N42"/>
+    <mergeCell ref="AP34:AP35"/>
+    <mergeCell ref="A35:A38"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="E35:K37"/>
+    <mergeCell ref="M35:N35"/>
+    <mergeCell ref="V35:W35"/>
+    <mergeCell ref="AJ35:AK35"/>
+    <mergeCell ref="B36:D38"/>
+    <mergeCell ref="M36:N36"/>
+    <mergeCell ref="V36:W36"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="G38:L38"/>
+    <mergeCell ref="AJ38:AK38"/>
+    <mergeCell ref="AO38:AR38"/>
+    <mergeCell ref="AJ36:AK36"/>
+    <mergeCell ref="AN36:AN37"/>
+    <mergeCell ref="AO36:AP37"/>
+    <mergeCell ref="AQ36:AR37"/>
+    <mergeCell ref="M43:N43"/>
+    <mergeCell ref="V43:W43"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="K47:W47"/>
+    <mergeCell ref="AJ47:AK47"/>
+    <mergeCell ref="AO39:AO40"/>
+    <mergeCell ref="AN41:AN42"/>
+    <mergeCell ref="AO41:AO42"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="K39:W39"/>
+    <mergeCell ref="X39:X41"/>
+    <mergeCell ref="Y39:Y41"/>
+    <mergeCell ref="Z39:Z41"/>
+    <mergeCell ref="AA39:AA41"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="K40:W40"/>
+    <mergeCell ref="AJ40:AK40"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="E41:H41"/>
+    <mergeCell ref="AJ41:AK41"/>
+    <mergeCell ref="AB39:AB41"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="E48:H48"/>
+    <mergeCell ref="AJ48:AK48"/>
+    <mergeCell ref="AB46:AB48"/>
+    <mergeCell ref="AC46:AC48"/>
+    <mergeCell ref="AJ46:AK46"/>
+    <mergeCell ref="A46:D46"/>
+    <mergeCell ref="K46:W46"/>
+    <mergeCell ref="X46:X48"/>
+    <mergeCell ref="Y46:Y48"/>
+    <mergeCell ref="Z46:Z48"/>
+    <mergeCell ref="AA46:AA48"/>
+    <mergeCell ref="A49:A52"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="E49:K51"/>
+    <mergeCell ref="M49:N49"/>
+    <mergeCell ref="V49:W49"/>
+    <mergeCell ref="AJ49:AK49"/>
+    <mergeCell ref="B50:D52"/>
+    <mergeCell ref="M50:N50"/>
+    <mergeCell ref="V50:W50"/>
+    <mergeCell ref="E52:F52"/>
+    <mergeCell ref="G52:L52"/>
+    <mergeCell ref="AJ52:AK52"/>
+    <mergeCell ref="AO52:AR52"/>
+    <mergeCell ref="L1:P1"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="U1:W1"/>
+    <mergeCell ref="Q1:T1"/>
+    <mergeCell ref="Y1:AB1"/>
+    <mergeCell ref="AC1:AG1"/>
+    <mergeCell ref="AJ50:AK50"/>
+    <mergeCell ref="AN50:AN51"/>
+    <mergeCell ref="AO50:AP51"/>
+    <mergeCell ref="M51:N51"/>
+    <mergeCell ref="V51:W51"/>
+    <mergeCell ref="AJ51:AK51"/>
+    <mergeCell ref="AP46:AP47"/>
+    <mergeCell ref="AL46:AM47"/>
+    <mergeCell ref="AN46:AN47"/>
+    <mergeCell ref="AO46:AO47"/>
+    <mergeCell ref="AN48:AN49"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="G45:L45"/>
+    <mergeCell ref="AJ45:AK45"/>
+    <mergeCell ref="AQ48:AQ49"/>
+    <mergeCell ref="AR48:AR49"/>
+    <mergeCell ref="AQ50:AQ51"/>
     <mergeCell ref="AR50:AR51"/>
     <mergeCell ref="AO48:AP49"/>
     <mergeCell ref="AI1:AK1"/>
@@ -4568,313 +4875,6 @@
     <mergeCell ref="V42:W42"/>
     <mergeCell ref="AJ42:AK42"/>
     <mergeCell ref="B43:D45"/>
-    <mergeCell ref="AO52:AR52"/>
-    <mergeCell ref="L1:P1"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="U1:W1"/>
-    <mergeCell ref="Q1:T1"/>
-    <mergeCell ref="Y1:AB1"/>
-    <mergeCell ref="AC1:AG1"/>
-    <mergeCell ref="AJ50:AK50"/>
-    <mergeCell ref="AN50:AN51"/>
-    <mergeCell ref="AO50:AP51"/>
-    <mergeCell ref="M51:N51"/>
-    <mergeCell ref="V51:W51"/>
-    <mergeCell ref="AJ51:AK51"/>
-    <mergeCell ref="AP46:AP47"/>
-    <mergeCell ref="AL46:AM47"/>
-    <mergeCell ref="AN46:AN47"/>
-    <mergeCell ref="AO46:AO47"/>
-    <mergeCell ref="AN48:AN49"/>
-    <mergeCell ref="E45:F45"/>
-    <mergeCell ref="G45:L45"/>
-    <mergeCell ref="AJ45:AK45"/>
-    <mergeCell ref="AQ48:AQ49"/>
-    <mergeCell ref="AR48:AR49"/>
-    <mergeCell ref="AQ50:AQ51"/>
-    <mergeCell ref="A49:A52"/>
-    <mergeCell ref="B49:D49"/>
-    <mergeCell ref="E49:K51"/>
-    <mergeCell ref="M49:N49"/>
-    <mergeCell ref="V49:W49"/>
-    <mergeCell ref="AJ49:AK49"/>
-    <mergeCell ref="B50:D52"/>
-    <mergeCell ref="M50:N50"/>
-    <mergeCell ref="V50:W50"/>
-    <mergeCell ref="E52:F52"/>
-    <mergeCell ref="G52:L52"/>
-    <mergeCell ref="AJ52:AK52"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="E48:H48"/>
-    <mergeCell ref="AJ48:AK48"/>
-    <mergeCell ref="AB46:AB48"/>
-    <mergeCell ref="AC46:AC48"/>
-    <mergeCell ref="AJ46:AK46"/>
-    <mergeCell ref="A46:D46"/>
-    <mergeCell ref="K46:W46"/>
-    <mergeCell ref="X46:X48"/>
-    <mergeCell ref="Y46:Y48"/>
-    <mergeCell ref="Z46:Z48"/>
-    <mergeCell ref="AA46:AA48"/>
-    <mergeCell ref="M43:N43"/>
-    <mergeCell ref="V43:W43"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="K47:W47"/>
-    <mergeCell ref="AJ47:AK47"/>
-    <mergeCell ref="AO39:AO40"/>
-    <mergeCell ref="AN41:AN42"/>
-    <mergeCell ref="AO41:AO42"/>
-    <mergeCell ref="A39:D39"/>
-    <mergeCell ref="K39:W39"/>
-    <mergeCell ref="X39:X41"/>
-    <mergeCell ref="Y39:Y41"/>
-    <mergeCell ref="Z39:Z41"/>
-    <mergeCell ref="AA39:AA41"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="K40:W40"/>
-    <mergeCell ref="AJ40:AK40"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="E41:H41"/>
-    <mergeCell ref="AJ41:AK41"/>
-    <mergeCell ref="AB39:AB41"/>
-    <mergeCell ref="AC39:AC41"/>
-    <mergeCell ref="AJ39:AK39"/>
-    <mergeCell ref="A42:A45"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="E42:K44"/>
-    <mergeCell ref="M42:N42"/>
-    <mergeCell ref="AP34:AP35"/>
-    <mergeCell ref="A35:A38"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="E35:K37"/>
-    <mergeCell ref="M35:N35"/>
-    <mergeCell ref="V35:W35"/>
-    <mergeCell ref="AJ35:AK35"/>
-    <mergeCell ref="B36:D38"/>
-    <mergeCell ref="M36:N36"/>
-    <mergeCell ref="V36:W36"/>
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="G38:L38"/>
-    <mergeCell ref="AJ38:AK38"/>
-    <mergeCell ref="AO38:AR38"/>
-    <mergeCell ref="AJ36:AK36"/>
-    <mergeCell ref="AN36:AN37"/>
-    <mergeCell ref="AO36:AP37"/>
-    <mergeCell ref="AQ36:AR37"/>
-    <mergeCell ref="M37:N37"/>
-    <mergeCell ref="V37:W37"/>
-    <mergeCell ref="AJ37:AK37"/>
-    <mergeCell ref="AP32:AP33"/>
-    <mergeCell ref="AQ32:AR35"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="K33:W33"/>
-    <mergeCell ref="AJ33:AK33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="E34:H34"/>
-    <mergeCell ref="AJ34:AK34"/>
-    <mergeCell ref="AB32:AB34"/>
-    <mergeCell ref="AC32:AC34"/>
-    <mergeCell ref="AJ32:AK32"/>
-    <mergeCell ref="AL32:AM33"/>
-    <mergeCell ref="AN32:AN33"/>
-    <mergeCell ref="AO32:AO33"/>
-    <mergeCell ref="AN34:AN35"/>
-    <mergeCell ref="AO34:AO35"/>
-    <mergeCell ref="A32:D32"/>
-    <mergeCell ref="K32:W32"/>
-    <mergeCell ref="X32:X34"/>
-    <mergeCell ref="Y32:Y34"/>
-    <mergeCell ref="Z32:Z34"/>
-    <mergeCell ref="AA32:AA34"/>
-    <mergeCell ref="AP27:AP28"/>
-    <mergeCell ref="A28:A31"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="E28:K30"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="V28:W28"/>
-    <mergeCell ref="AJ28:AK28"/>
-    <mergeCell ref="B29:D31"/>
-    <mergeCell ref="M29:N29"/>
-    <mergeCell ref="V29:W29"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="G31:L31"/>
-    <mergeCell ref="AJ31:AK31"/>
-    <mergeCell ref="AO31:AR31"/>
-    <mergeCell ref="AJ29:AK29"/>
-    <mergeCell ref="AN29:AN30"/>
-    <mergeCell ref="AO29:AP30"/>
-    <mergeCell ref="AQ29:AR30"/>
-    <mergeCell ref="M30:N30"/>
-    <mergeCell ref="V30:W30"/>
-    <mergeCell ref="AJ30:AK30"/>
-    <mergeCell ref="AP25:AP26"/>
-    <mergeCell ref="AQ25:AR28"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="K26:W26"/>
-    <mergeCell ref="AJ26:AK26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:H27"/>
-    <mergeCell ref="AJ27:AK27"/>
-    <mergeCell ref="AB25:AB27"/>
-    <mergeCell ref="AC25:AC27"/>
-    <mergeCell ref="AJ25:AK25"/>
-    <mergeCell ref="AL25:AM26"/>
-    <mergeCell ref="AN25:AN26"/>
-    <mergeCell ref="AO25:AO26"/>
-    <mergeCell ref="AN27:AN28"/>
-    <mergeCell ref="AO27:AO28"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="K25:W25"/>
-    <mergeCell ref="X25:X27"/>
-    <mergeCell ref="Y25:Y27"/>
-    <mergeCell ref="Z25:Z27"/>
-    <mergeCell ref="AA25:AA27"/>
-    <mergeCell ref="AP20:AP21"/>
-    <mergeCell ref="A21:A24"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="E21:K23"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="V21:W21"/>
-    <mergeCell ref="AJ21:AK21"/>
-    <mergeCell ref="B22:D24"/>
-    <mergeCell ref="M22:N22"/>
-    <mergeCell ref="V22:W22"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="G24:L24"/>
-    <mergeCell ref="AJ24:AK24"/>
-    <mergeCell ref="AO24:AR24"/>
-    <mergeCell ref="AJ22:AK22"/>
-    <mergeCell ref="AN22:AN23"/>
-    <mergeCell ref="AO22:AP23"/>
-    <mergeCell ref="AQ22:AR23"/>
-    <mergeCell ref="M23:N23"/>
-    <mergeCell ref="V23:W23"/>
-    <mergeCell ref="AJ23:AK23"/>
-    <mergeCell ref="AP18:AP19"/>
-    <mergeCell ref="AQ18:AR21"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="K19:W19"/>
-    <mergeCell ref="AJ19:AK19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:H20"/>
-    <mergeCell ref="AJ20:AK20"/>
-    <mergeCell ref="AB18:AB20"/>
-    <mergeCell ref="AC18:AC20"/>
-    <mergeCell ref="AJ18:AK18"/>
-    <mergeCell ref="AL18:AM19"/>
-    <mergeCell ref="AN18:AN19"/>
-    <mergeCell ref="AO18:AO19"/>
-    <mergeCell ref="AN20:AN21"/>
-    <mergeCell ref="AO20:AO21"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="K18:W18"/>
-    <mergeCell ref="X18:X20"/>
-    <mergeCell ref="Y18:Y20"/>
-    <mergeCell ref="Z18:Z20"/>
-    <mergeCell ref="AA18:AA20"/>
-    <mergeCell ref="AP13:AP14"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="E14:K16"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="V14:W14"/>
-    <mergeCell ref="AJ14:AK14"/>
-    <mergeCell ref="B15:D17"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="V15:W15"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:L17"/>
-    <mergeCell ref="AJ17:AK17"/>
-    <mergeCell ref="AO17:AR17"/>
-    <mergeCell ref="AJ15:AK15"/>
-    <mergeCell ref="AN15:AN16"/>
-    <mergeCell ref="AO15:AP16"/>
-    <mergeCell ref="AQ15:AR16"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="V16:W16"/>
-    <mergeCell ref="AJ16:AK16"/>
-    <mergeCell ref="AP11:AP12"/>
-    <mergeCell ref="AQ11:AR14"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="K12:W12"/>
-    <mergeCell ref="AJ12:AK12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="E13:H13"/>
-    <mergeCell ref="AJ13:AK13"/>
-    <mergeCell ref="AB11:AB13"/>
-    <mergeCell ref="AC11:AC13"/>
-    <mergeCell ref="AJ11:AK11"/>
-    <mergeCell ref="AL11:AM12"/>
-    <mergeCell ref="AN11:AN12"/>
-    <mergeCell ref="AO11:AO12"/>
-    <mergeCell ref="AN13:AN14"/>
-    <mergeCell ref="AO13:AO14"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="K11:W11"/>
-    <mergeCell ref="X11:X13"/>
-    <mergeCell ref="Y11:Y13"/>
-    <mergeCell ref="Z11:Z13"/>
-    <mergeCell ref="AA11:AA13"/>
-    <mergeCell ref="AQ4:AR7"/>
-    <mergeCell ref="AQ8:AR9"/>
-    <mergeCell ref="AO10:AR10"/>
-    <mergeCell ref="AO4:AO5"/>
-    <mergeCell ref="AP4:AP5"/>
-    <mergeCell ref="AO6:AO7"/>
-    <mergeCell ref="AP6:AP7"/>
-    <mergeCell ref="AO8:AP9"/>
-    <mergeCell ref="AJ7:AK7"/>
-    <mergeCell ref="AJ8:AK8"/>
-    <mergeCell ref="AJ9:AK9"/>
-    <mergeCell ref="AJ10:AK10"/>
-    <mergeCell ref="AL4:AM5"/>
-    <mergeCell ref="AN4:AN5"/>
-    <mergeCell ref="AN6:AN7"/>
-    <mergeCell ref="AN8:AN9"/>
-    <mergeCell ref="AH3:AI3"/>
-    <mergeCell ref="AJ3:AK3"/>
-    <mergeCell ref="AL3:AM3"/>
-    <mergeCell ref="AJ4:AK4"/>
-    <mergeCell ref="AJ5:AK5"/>
-    <mergeCell ref="AJ6:AK6"/>
-    <mergeCell ref="X4:X6"/>
-    <mergeCell ref="Y4:Y6"/>
-    <mergeCell ref="Z4:Z6"/>
-    <mergeCell ref="AA4:AA6"/>
-    <mergeCell ref="AB4:AB6"/>
-    <mergeCell ref="AC4:AC6"/>
-    <mergeCell ref="V7:W7"/>
-    <mergeCell ref="V8:W8"/>
-    <mergeCell ref="V9:W9"/>
-    <mergeCell ref="E6:H6"/>
-    <mergeCell ref="E7:K9"/>
-    <mergeCell ref="G10:L10"/>
-    <mergeCell ref="K4:W4"/>
-    <mergeCell ref="K5:W5"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="M9:N9"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="A7:A10"/>
-    <mergeCell ref="B8:D10"/>
-    <mergeCell ref="E10:F10"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0.15748031496062992" bottom="0" header="0" footer="0.31496062992125984"/>
